--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,576 +458,346 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>311307</v>
+        <v>301843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
+          <t>CAMPARI 998ML</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15.99</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>303488</v>
+        <v>215568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>115.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>323487</v>
+        <v>174010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAMARAO COSTA SUL 300G VAN  SEM CABEÇA COZIDO</t>
+          <t>CACHAÇA SELETA 600ML</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29.99</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>262170</v>
+        <v>287369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>141831</v>
+        <v>170451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FILÉ DE PANGA KG</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>315711</v>
+        <v>247800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA DO PESCADO 500G</t>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>203263</v>
+        <v>177250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA KG</t>
+          <t>CERVEJA DEVASSA 12 X 269ML PURO MALTE</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>323489</v>
+        <v>303283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>323501</v>
+        <v>286362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FILÉ DE SALMAO COSTA SUL 400G COM PELE</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>254014</v>
+        <v>108686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FILÉ DE DOURADA VITÓRIA PESCADOS 1KG</t>
+          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>284245</v>
+        <v>155994</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PEIXITOS COSTA SUL 300G</t>
+          <t xml:space="preserve">VINHO GALIOTTO 1L TINTO SECO </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>284246</v>
+        <v>139964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+          <t xml:space="preserve">VINHO PERGOLA 1L  TINTO SUAVE </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105461</v>
+        <v>110373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BISTECA DO CONTRA FILE KG</t>
+          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>31.99</v>
+        <v>83.98999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>105458</v>
+        <v>248750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18.99</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>105451</v>
+        <v>102077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>105449</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>COXÃO DURO KG</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>105453</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FILE MIGNON KG</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>40.99</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>105474</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FRALDINHA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>305039</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LINGUICA BOVINA  CASEIRA KG</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>106053</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA CARRE KG</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>105062</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>106054</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LOMBO SUINO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>106052</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>106034</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SUAN SUINA KG</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>106032</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TOUCINHO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>19.99</v>
+        <v>179.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,167 @@
         <v>179.99</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>105450</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ALCATRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>105456</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA  CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MUSCULO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,273 +458,273 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>301843</v>
+        <v>105842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAMPARI 998ML</t>
+          <t>ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78.98999999999999</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>215568</v>
+        <v>227503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>174010</v>
+        <v>105838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CACHAÇA SELETA 600ML</t>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45.99</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>287369</v>
+        <v>105840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.59</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>170451</v>
+        <v>306504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>247800</v>
+        <v>109597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>FILE DE PEITO DE FRANGO KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.69</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>177250</v>
+        <v>108786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CERVEJA DEVASSA 12 X 269ML PURO MALTE</t>
+          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.79</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>303283</v>
+        <v>108788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>286362</v>
+        <v>105853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
+          <t>FRANGO MARINGA CONGELADO KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.49</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>108686</v>
+        <v>185934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
+          <t>GALINHA NOROESTE CONGELADA KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>155994</v>
+        <v>228422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINHO GALIOTTO 1L TINTO SECO </t>
+          <t xml:space="preserve">LINGUICA SUPER FRANGO  GROSSA KG </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>26.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>139964</v>
+        <v>108774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINHO PERGOLA 1L  TINTO SUAVE </t>
+          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -734,76 +734,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110373</v>
+        <v>108773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
+          <t>MOELA DE FRANGO SADIA  BDJ 1KG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>83.98999999999999</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>248750</v>
+        <v>105770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
+          <t>MORTADELA PERDIGÃO  FRANGO KG</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>102077</v>
+        <v>105460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
+          <t>BISTECA BOVINA KG  PALETA</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>179.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -835,21 +835,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>105450</v>
+        <v>158997</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ALCATRA BOVINA KG</t>
+          <t>BISTECA BOVINA KG ACEM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -858,21 +858,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105456</v>
+        <v>105458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>CHAMBARI KG</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>105474</v>
+        <v>115278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FRALDINHA BOVINA KG</t>
+          <t>MIOLO DA PALETA KG BOVINA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -904,44 +904,44 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>107260</v>
+        <v>231292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>28.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>305039</v>
+        <v>105469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA  CASEIRA KG</t>
+          <t>PALETA BOVINA KG</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>15.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -959,6 +959,1156 @@
       </c>
       <c r="E23" t="n">
         <v>21.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>106032</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TOUCINHO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>255232</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>298736</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>298239</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AÇUCAR ECOÇUCAR CRISTAL  2KG</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>107878</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>179914</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>136523</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>100020</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>199440</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>111378</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AZEITONAS LA VIOLETERA 160GR VERDES FATIADAS</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>250013</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>102085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CACHACA 51 965ML</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>101137</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>170451</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>298701</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>184034</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>101063</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>110330</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>100391</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>100394</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>100392</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>100402</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>100403</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>100393</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>100390</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>102282</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>273714</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>128930</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>100024</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>279573</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>255841</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FLOCÃO DE MILHO AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>108434</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>231627</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE EM PO CAMPONESA 1KG INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>101113</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>290255</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MACARRAO CRISTAL 500G SEMOLA ESPAGUETE</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>101728</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>130920</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>100054</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OLEO DE SOJA BREJEIRO 900ML</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>104404</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>104410</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>239315</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>289451</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>228234</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>100706</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>221089</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO 125G OLEO</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>100373</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 SUCO</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>102237</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA VIDRO 1,5L  INTEGRAL TINTO</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>106961</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3.29</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,628 +458,588 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105842</v>
+        <v>255232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>227503</v>
+        <v>298239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL  2KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.99</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105838</v>
+        <v>100431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.89</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - AVE</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>105840</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
-        </is>
-      </c>
+        <v>116139</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>14.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - AVE</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>306504</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FIGADO DE FRANGO PERDIGAO KG</t>
-        </is>
-      </c>
+        <v>107395</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>109597</v>
+        <v>225670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
+          <t>ARROZ BENTO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108786</v>
+        <v>100038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30.99</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108788</v>
+        <v>136523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.99</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - AVE</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>105853</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
-        </is>
-      </c>
+        <v>234617</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>11.29</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - AVE</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>185934</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GALINHA NOROESTE CONGELADA KG</t>
-        </is>
-      </c>
+        <v>199869</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>8.99</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>228422</v>
+        <v>102085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SUPER FRANGO  GROSSA KG </t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.99</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>108774</v>
+        <v>101137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>108773</v>
+        <v>170451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA  BDJ 1KG</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>105770</v>
+        <v>247800</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MORTADELA PERDIGÃO  FRANGO KG</t>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>105460</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BISTECA BOVINA KG  PALETA</t>
-        </is>
-      </c>
+        <v>239382</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>19.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>105470</v>
+        <v>298701</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158997</v>
+        <v>184034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG ACEM</t>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105458</v>
+        <v>324556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>115278</v>
+        <v>101063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIOLO DA PALETA KG BOVINA</t>
+          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26.99</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>231292</v>
+        <v>112978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIOLO DO ACEM KG</t>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105469</v>
+        <v>134193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PALETA BOVINA KG</t>
+          <t>DESINFETANTE YPE BAK 2L FLORAL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>105475</v>
+        <v>100391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>106034</v>
+        <v>100394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>106032</v>
+        <v>100392</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>255232</v>
+        <v>100402</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>298736</v>
+        <v>100403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>298239</v>
+        <v>100393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL  2KG</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8.390000000000001</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1088,182 +1048,166 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>107878</v>
+        <v>100390</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>179914</v>
+        <v>102282</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>11.49</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>136523</v>
+        <v>273714</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100020</v>
+        <v>100024</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>199440</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
-        </is>
-      </c>
+        <v>100014</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>27.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>111378</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>AZEITONAS LA VIOLETERA 160GR VERDES FATIADAS</t>
-        </is>
-      </c>
+        <v>100119</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>12.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250013</v>
+        <v>139059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+          <t>LAVA LOUÇAS LIQUIDO YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102085</v>
+        <v>108434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1272,90 +1216,90 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>101137</v>
+        <v>101113</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>170451</v>
+        <v>106922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.79</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>298701</v>
+        <v>131884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.09</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>184034</v>
+        <v>101726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1364,113 +1308,113 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>101063</v>
+        <v>130920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.69</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>110330</v>
+        <v>106680</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.19</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>100391</v>
+        <v>128920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>100394</v>
+        <v>104404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>100392</v>
+        <v>104406</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1479,21 +1423,21 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>100402</v>
+        <v>261360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
+          <t>SABÃO EM BARRA MINUANO 900G NEUTRO GLICERINADO</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1502,90 +1446,90 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>100403</v>
+        <v>228234</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>100393</v>
+        <v>100705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
+          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G TOMATE </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100390</v>
+        <v>100693</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
+          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G OLEO </t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>102282</v>
+        <v>100373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.69</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1594,21 +1538,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>273714</v>
+        <v>100876</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1617,498 +1561,536 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>128930</v>
+        <v>106961</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
+          <t>QUARTA - OFERTAS 16/04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>100024</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
-        </is>
-      </c>
+        <v>106960</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>279573</v>
+        <v>104937</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>255841</v>
+        <v>105023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FLOCÃO DE MILHO AMAFIL 500G</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.89</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>108434</v>
+        <v>105010</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>231627</v>
+        <v>105001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CAMPONESA 1KG INTEGRAL </t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>39.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>101113</v>
+        <v>104919</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>290255</v>
+        <v>104862</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MACARRAO CRISTAL 500G SEMOLA ESPAGUETE</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>101728</v>
+        <v>104931</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>12.99</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>130920</v>
+        <v>104944</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>100054</v>
+        <v>104928</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA BREJEIRO 900ML</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8.390000000000001</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>104404</v>
+        <v>104947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9.49</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>104410</v>
+        <v>104996</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>104406</v>
+        <v>239921</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10.49</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>239315</v>
+        <v>104992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>289451</v>
+        <v>104961</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>27.99</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>228234</v>
+        <v>105470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+          <t>ACEM BOVINO KG</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>13.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>100706</v>
+        <v>105459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.59</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>221089</v>
+        <v>105449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125G OLEO</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5.59</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100373</v>
+        <v>107260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 SUCO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>102237</v>
+        <v>115278</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SUCO DE UVA AURORA VIDRO 1,5L  INTEGRAL TINTO</t>
+          <t>MIOLO DA PALETA KG BOVINA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>27.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>106961</v>
+        <v>231292</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+          <t>MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3.29</v>
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA  CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -530,11 +530,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
       <c r="C5" t="n">
         <v>116139</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>7.99</v>
       </c>
@@ -545,11 +553,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>107395</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+        </is>
+      </c>
       <c r="E6" t="n">
         <v>7.99</v>
       </c>
@@ -629,11 +645,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
       <c r="C10" t="n">
         <v>234617</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BISCOITO ESTRELA 350G CREAM CRACKER</t>
+        </is>
+      </c>
       <c r="E10" t="n">
         <v>5.19</v>
       </c>
@@ -644,11 +668,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>199869</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>7.79</v>
       </c>
@@ -751,11 +783,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>239382</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CERVEJA DEVASSA 269ML PURO MALTE</t>
+        </is>
+      </c>
       <c r="E16" t="n">
         <v>2.69</v>
       </c>
@@ -1134,11 +1174,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
       <c r="C33" t="n">
         <v>100014</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FEIJAO GOL 1KG CORES</t>
+        </is>
+      </c>
       <c r="E33" t="n">
         <v>5.99</v>
       </c>
@@ -1149,11 +1197,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
       <c r="C34" t="n">
         <v>100119</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FLOCAO MILHO SINHA 500G</t>
+        </is>
+      </c>
       <c r="E34" t="n">
         <v>2.89</v>
       </c>
@@ -1578,11 +1634,19 @@
           <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
       <c r="C53" t="n">
         <v>106960</v>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
       <c r="E53" t="n">
         <v>3.99</v>
       </c>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,812 +458,812 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105842</v>
+        <v>255232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>227503</v>
+        <v>298239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105838</v>
+        <v>100426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t>AGUA SANITARIA QBOA 1L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.89</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105840</v>
+        <v>207640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t>AGUA SANITARIA LAVABEM 2L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14.59</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>306504</v>
+        <v>133368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIGADO DE FRANGO PERDIGAO KG</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>109597</v>
+        <v>181416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
+          <t>AMACINATE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108786</v>
+        <v>107394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L CARINHO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108788</v>
+        <v>107393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>105853</v>
+        <v>106711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L ACONCHEGO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11.29</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>185934</v>
+        <v>106712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GALINHA NOROESTE CONGELADA KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L TERNURA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>228422</v>
+        <v>107413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SUPER FRANGO  GROSSA KG </t>
+          <t>AMACIANTE DE ROUPAS YPE 2L DELICADO BRANCO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>108774</v>
+        <v>179914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
+          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>108773</v>
+        <v>245393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA  BDJ 1KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>105770</v>
+        <v>100037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MORTADELA PERDIGÃO  FRANGO KG</t>
+          <t>ARROZ PAINHO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>105460</v>
+        <v>100040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG  PALETA</t>
+          <t>ARROZ TIO JORGE PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>105470</v>
+        <v>113480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
+          <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158997</v>
+        <v>132657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG ACEM</t>
+          <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105458</v>
+        <v>123206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t xml:space="preserve">AZEITONAS LA VIOLETERA SACHÊ 160G FATIADA </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>18.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>115278</v>
+        <v>250013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIOLO DA PALETA KG BOVINA</t>
+          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>231292</v>
+        <v>239682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIOLO DO ACEM KG</t>
+          <t xml:space="preserve">BOMBOM GAROTO CAIXA 250G SORTIDO </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>25.99</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105469</v>
+        <v>237036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PALETA BOVINA KG</t>
+          <t xml:space="preserve">BOMBOM NESTLE 251G ESPECIALIDADES </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>105475</v>
+        <v>181622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t xml:space="preserve">BOMBONS LACTA 250,6G FAVORITOS </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21.99</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>106034</v>
+        <v>114037</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>106032</v>
+        <v>239446</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>255232</v>
+        <v>242930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>298736</v>
+        <v>303283</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>298239</v>
+        <v>324556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL  2KG</t>
+          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8.390000000000001</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>107878</v>
+        <v>295198</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t xml:space="preserve">CHOPP DE VINHO STEMPEL 600ML RED </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>179914</v>
+        <v>101066</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
+          <t>CREME DE LEITE ITALAC 200G</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>11.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>136523</v>
+        <v>247502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">DESINFETANTE +FAMILIA 5L LAVANDA </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100020</v>
+        <v>207582</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>199440</v>
+        <v>256724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>111378</v>
+        <v>207588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AZEITONAS LA VIOLETERA 160GR VERDES FATIADAS</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250013</v>
+        <v>207586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102085</v>
+        <v>207584</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>11.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1272,90 +1272,90 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>101137</v>
+        <v>100780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>170451</v>
+        <v>134629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.79</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>298701</v>
+        <v>200178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t>FEIJÃO DONA DE 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.09</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>184034</v>
+        <v>100120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1364,21 +1364,21 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>101063</v>
+        <v>155080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+          <t>LEITE CONDENSADO LEITBOM 395G</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.69</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1387,67 +1387,67 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>110330</v>
+        <v>231627</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
+          <t xml:space="preserve">LEITE EM PO CAMPONESA 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.19</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>100391</v>
+        <v>170363</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>100394</v>
+        <v>183340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
+          <t>LEITE ITALAC 1L UHT SEMI DESNATADO</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1456,136 +1456,136 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>100392</v>
+        <v>156422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
+          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>100402</v>
+        <v>101728</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>100403</v>
+        <v>108414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
+          <t>MASSA PARA LASANHA CRISTAL 500G</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>100393</v>
+        <v>302126</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
+          <t>MASSA PARA TAPIOCA DONA DE 1KG HIDRATADA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100390</v>
+        <v>107640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
+          <t>MILHO VERDE QUERO LATA 170G</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>102282</v>
+        <v>101130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t xml:space="preserve">MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.69</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>273714</v>
+        <v>321107</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+          <t xml:space="preserve">MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1617,21 +1617,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>128930</v>
+        <v>244444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
+          <t>MOLHO DE TOMATE DEZ 300G TRADICIONAL</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1640,113 +1640,113 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>100024</v>
+        <v>100754</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+          <t>PALMITO PERIQUITU 300G ACAI INTEIRO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>279573</v>
+        <v>236651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+          <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>255841</v>
+        <v>104404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FLOCÃO DE MILHO AMAFIL 500G</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.89</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>108434</v>
+        <v>104410</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>231627</v>
+        <v>104406</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CAMPONESA 1KG INTEGRAL </t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>39.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1755,67 +1755,67 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>101113</v>
+        <v>239315</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
+          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>290255</v>
+        <v>286199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MACARRAO CRISTAL 500G SEMOLA ESPAGUETE</t>
+          <t xml:space="preserve">SABÃO EM PO TIXAN YPE CAIXA 800G MACIEZ </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>101728</v>
+        <v>261083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+          <t>SABÃO EM PO TIXAN YPE CAIXA 800G PRIMAVERA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>12.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1824,291 +1824,613 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>130920</v>
+        <v>100706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>100054</v>
+        <v>221089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA BREJEIRO 900ML</t>
+          <t>SARDINHA COQUEIRO 125G OLEO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8.390000000000001</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>104404</v>
+        <v>100373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#05 BEBIDA - #00 SUCO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>104410</v>
+        <v>102237</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
+          <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>104406</v>
+        <v>100876</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>239315</v>
+        <v>155994</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
+          <t xml:space="preserve">VINHO GALIOTTO 1L TINTO SECO </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>289451</v>
+        <v>139964</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
+          <t xml:space="preserve">VINHO PERGOLA 1L TINTO SUAVE </t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>27.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>228234</v>
+        <v>311307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>100706</v>
+        <v>303488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.59</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>221089</v>
+        <v>323487</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125G OLEO</t>
+          <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5.59</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100373</v>
+        <v>262170</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 SUCO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>102237</v>
+        <v>141831</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SUCO DE UVA AURORA VIDRO 1,5L  INTEGRAL TINTO</t>
+          <t>FILÉ DE PANGA KG</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>27.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>106961</v>
+        <v>315711</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+          <t>FILÉ DE TILAPIA DO PESCADO 500G</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3.29</v>
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>323489</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>323501</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FILÉ DE SALMAO COSTA SUL 400G COM PELE</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>284245</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PEIXITOS COSTA SUL 300G</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>284246</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>105468</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>106053</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>320822</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BISTECA SUINA KG PALETA FRESCA </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>106054</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LOMBO SUINO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>106052</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PELE SUINA KG</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,651 +458,651 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>255232</v>
+        <v>157014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>298239</v>
+        <v>152232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL  2KG</t>
+          <t>BUCHO BOVINO KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.289999999999999</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100431</v>
+        <v>105458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 2L</t>
+          <t>CHAMBARI KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116139</v>
+        <v>105451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>107395</v>
+        <v>105471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>COSTELA BOVINA KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>225670</v>
+        <v>105449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ARROZ BENTO PCT 5KG TIPO 1 BRANCO</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100038</v>
+        <v>107260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35.69</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>136523</v>
+        <v>305039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33.29</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>234617</v>
+        <v>189031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BISCOITO ESTRELA 350G CREAM CRACKER</t>
+          <t>LINGUICA FRICO MISTA KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.19</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>199869</v>
+        <v>105475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
+          <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.79</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>102085</v>
+        <v>105062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.59</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101137</v>
+        <v>105433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170451</v>
+        <v>106052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>PELE SUINA KG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.79</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>247800</v>
+        <v>229014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>AGUA DE COCO MAIS COCO 1L</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>239382</v>
+        <v>215568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CERVEJA DEVASSA 269ML PURO MALTE</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.69</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>298701</v>
+        <v>174010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t>CACHAÇA SELETA 600ML</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>184034</v>
+        <v>158451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t>CACHAÇA YPIOCA  965ML PRATA SEM PALHA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.89</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>324556</v>
+        <v>170451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>101063</v>
+        <v>247800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>112978</v>
+        <v>267604</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500G</t>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LONG NECK</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>134193</v>
+        <v>184034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPE BAK 2L FLORAL</t>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100391</v>
+        <v>309102</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100394</v>
+        <v>298123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100392</v>
+        <v>259153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
+          <t>CERVEJA SPATEN 12 X 350ML PURO MALTE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.69</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100402</v>
+        <v>244424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100403</v>
+        <v>253877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>100393</v>
+        <v>253878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100390</v>
+        <v>253880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1111,1050 +1111,245 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>102282</v>
+        <v>244426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8.789999999999999</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>273714</v>
+        <v>305261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+          <t>ENERGETICO BALY 2L ABACAXI COM HORTELA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100024</v>
+        <v>320467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>100014</v>
+        <v>302661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FEIJAO GOL 1KG CORES</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L MORANGO E PESSEGO </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100119</v>
+        <v>302660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SINHA 500G</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L TANGERINA </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.89</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>139059</v>
+        <v>303008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LAVA LOUÇAS LIQUIDO YPE 500ML LIMAO</t>
+          <t>ENERGETICO BALY 2L ENERGY CRANBERRY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>108434</v>
+        <v>102287</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+          <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>101113</v>
+        <v>161871</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
+          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>106922</v>
+        <v>134156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
+          <t>VODKA SKYY 980ML</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - PREÇO BALA 17/04/25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>131884</v>
+        <v>100038</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.49</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - PREÇO BALA 17/04/25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>101726</v>
+        <v>106680</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>8.99</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>130920</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>106680</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>9.59</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>128920</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>104404</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>104406</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>261360</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SABÃO EM BARRA MINUANO 900G NEUTRO GLICERINADO</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>228234</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>100705</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G TOMATE </t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>100693</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G OLEO </t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>100373</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>100876</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>106961</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>106960</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>104937</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>105023</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>105010</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>104919</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>104931</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>8.890000000000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>MACA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>MANGA PALMER KG</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>104947</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>104996</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>MELAO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>239921</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>104992</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>REPOLHO VERDE KG</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>104961</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>9.390000000000001</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>105470</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ACEM BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>105459</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>105449</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>COXÃO DURO KG</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>30.99</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>107260</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>MAÇÃ DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>115278</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MIOLO DA PALETA KG BOVINA</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>231292</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MIOLO DO ACEM KG</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>305039</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LINGUICA BOVINA  CASEIRA KG</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>106034</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SUAN SUINA KG</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,213 @@
         <v>8.99</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>105010</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>105001</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>104855</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>104962</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MARACUJA AZEDO KG</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,898 +458,1795 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157014</v>
+        <v>105842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
+          <t>ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13.99</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>152232</v>
+        <v>227503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105458</v>
+        <v>105838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105451</v>
+        <v>105840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.99</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105471</v>
+        <v>306504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>105449</v>
+        <v>108786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>107260</v>
+        <v>108788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>305039</v>
+        <v>225767</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>FRANGO BONASA CONGELADO KG</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>189031</v>
+        <v>185934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LINGUICA FRICO MISTA KG</t>
+          <t>GALINHA NOROESTE CONGELADA KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>105475</v>
+        <v>228422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105062</v>
+        <v>309350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>MASSA DE PASTEL JK 1KG</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>105433</v>
+        <v>309331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t xml:space="preserve">MASSA DE PASTEL JK 500G DISCAO </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>106052</v>
+        <v>309332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
+          <t xml:space="preserve">MASSA DE PASTEL JK 500G ROLO </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>229014</v>
+        <v>108774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AGUA DE COCO MAIS COCO 1L</t>
+          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>215568</v>
+        <v>108773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>174010</v>
+        <v>157014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CACHAÇA SELETA 600ML</t>
+          <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158451</v>
+        <v>105470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CACHAÇA YPIOCA  965ML PRATA SEM PALHA</t>
+          <t>ACEM BOVINO KG</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>29.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>170451</v>
+        <v>105456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.79</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>247800</v>
+        <v>105463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>CORAÇÃO BOVINO KG</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>267604</v>
+        <v>105449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LONG NECK</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>184034</v>
+        <v>105487</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t xml:space="preserve">CUPIM BOVINO KG </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>309102</v>
+        <v>305039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.19</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>298123</v>
+        <v>105475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK</t>
+          <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.19</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>259153</v>
+        <v>320822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 12 X 350ML PURO MALTE</t>
+          <t xml:space="preserve">BISTECA SUINA KG PALETA FRESCA </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.59</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>244424</v>
+        <v>106054</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
+          <t>LOMBO SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>253877</v>
+        <v>106034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
+          <t>SUAN SUINA KG</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>253878</v>
+        <v>255232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>253880</v>
+        <v>298239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>15.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>244426</v>
+        <v>100426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
+          <t>AGUA SANITARIA QBOA 1L</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15.99</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>305261</v>
+        <v>116139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ABACAXI COM HORTELA</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15.99</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>320467</v>
+        <v>107395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15.99</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>302661</v>
+        <v>225670</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L MORANGO E PESSEGO </t>
+          <t>ARROZ BENTO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>302660</v>
+        <v>325990</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L TANGERINA </t>
+          <t xml:space="preserve">ARROZ FLORA PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>303008</v>
+        <v>258938</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ENERGY CRANBERRY</t>
+          <t xml:space="preserve">ARROZ BRILHANTE PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102287</v>
+        <v>100031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
+          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>161871</v>
+        <v>261728</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
+          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>134156</v>
+        <v>199869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VODKA SKYY 980ML</t>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>59.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100038</v>
+        <v>239682</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">BOMBOM GAROTO CAIXA 250G SORTIDO </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>101137</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>287369</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>170451</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>249597</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA HEINEKEN 330ML ZERO ALCOOL </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>242930</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 330ML</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - FERMENTADOS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>295198</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHOPP DE VINHO STEMPEL 600ML RED </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>155079</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE LEITBOM 200G</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>112978</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>247502</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESINFETANTE +FAMILIA 5L LAVANDA </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>100423</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>100419</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>220037</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>204461</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>100417</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>106661</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>102282</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>273714</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>128930</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FARINHA DE MANDIOCA AMAFIL 1KG AMARELA OURO</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>100024</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>167687</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>FEIJÃO JOAOZINHO 1KG CARIOCA PREMIUM</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>255841</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FLOCÃO DE MILHO AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>108434</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>170363</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>307145</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>303196</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>101726</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>130920</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>244444</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MOLHO DE TOMATE DEZ 300G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C69" t="n">
         <v>106680</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E69" t="n">
         <v>8.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>236651</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>104404</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>108686</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>150356</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SABÃO LIQUIDO OMO 3L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>286199</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABÃO EM PO TIXAN YPE CAIXA 800G MACIEZ </t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>261083</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SABÃO EM PO TIXAN YPE CAIXA 800G PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>100876</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>106961</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>106960</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,1105 +458,2163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157014</v>
+        <v>255232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>152232</v>
+        <v>298239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105458</v>
+        <v>100431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105451</v>
+        <v>133368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.99</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105471</v>
+        <v>269680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t xml:space="preserve">ARROZ DONA VAVA PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>105449</v>
+        <v>136523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>107260</v>
+        <v>100020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>305039</v>
+        <v>186826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t xml:space="preserve">BISCOITO GALLO 360G CREAM CRACKER </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.99</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>189031</v>
+        <v>315855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LINGUICA FRICO MISTA KG</t>
+          <t>BISCOITO RENATA 360G COCO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.99</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>105475</v>
+        <v>102085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.99</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105062</v>
+        <v>114037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18.99</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>105433</v>
+        <v>242311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>106052</v>
+        <v>287369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>229014</v>
+        <v>298701</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AGUA DE COCO MAIS COCO 1L</t>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>215568</v>
+        <v>184034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>174010</v>
+        <v>324556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CACHAÇA SELETA 600ML</t>
+          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158451</v>
+        <v>107928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CACHAÇA YPIOCA  965ML PRATA SEM PALHA</t>
+          <t xml:space="preserve">CREME DENTAL COLGATE 180G MPA </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>29.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>170451</v>
+        <v>101063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.79</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>247800</v>
+        <v>208281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>267604</v>
+        <v>208304</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LONG NECK</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML PROTECT UNISSEX </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>184034</v>
+        <v>208280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>309102</v>
+        <v>247502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
+          <t xml:space="preserve">DESINFETANTE +FAMILIA 5L LAVANDA </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.19</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>298123</v>
+        <v>312369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML ENERGY MEN </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>259153</v>
+        <v>312371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 12 X 350ML PURO MALTE</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO FLOR LAVANDA </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>244424</v>
+        <v>312370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>253877</v>
+        <v>312366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE PROTECT </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>253878</v>
+        <v>312367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FRUTAS VERMELHA </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>253880</v>
+        <v>312368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML POWER MEN </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>244426</v>
+        <v>298929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN GIRL </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>305261</v>
+        <v>298928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ABACAXI COM HORTELA</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN SPORT </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>320467</v>
+        <v>298927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN BOY </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>302661</v>
+        <v>298933</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L MORANGO E PESSEGO </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML INVISIBLE CARE </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>302660</v>
+        <v>298932</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L TANGERINA </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN SPORT </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>303008</v>
+        <v>298931</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ENERGY CRANBERRY</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML UNISSEX SPORT </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102287</v>
+        <v>298930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML SEM PERFUME </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>161871</v>
+        <v>311881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATAÇÃO INTENSA </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>134156</v>
+        <v>100423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VODKA SKYY 980ML</t>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>59.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100038</v>
+        <v>100419</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>106680</v>
+        <v>220037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>105010</v>
+        <v>204461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>105001</v>
+        <v>100420</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>104862</v>
+        <v>100417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>104931</v>
+        <v>106661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>104855</v>
+        <v>312365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LIMAO TAITI KG</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FLOR DE ALGODAO WOMEN </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>104962</v>
+        <v>312364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MARACUJA AZEDO KG</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML IMPACT MEN </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>104947</v>
+        <v>102287</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>104992</v>
+        <v>273714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.39</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>104961</v>
+        <v>155501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
         </is>
       </c>
       <c r="E49" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>286381</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FEIJÃO DONA DE 1KG PRETO</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>163918</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FEIJÃO KICALDO 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>100119</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FLOCÃO DE MILHO SINHA 500G</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>113183</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LEITE COND MARAJOARA 395G SEMIDESNATADO</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>170363</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>106922</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>43.99</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>183340</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LEITE ITALAC 1L UHT SEMI DESNATADO</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>131884</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>101728</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>169708</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASSA PARA TAPIOCA DO ZE 500G PRONTA </t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>107640</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MILHO VERDE QUERO LATA 170G</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>321107</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>106680</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OLEO DE SOJA SOYA 900ML</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>145874</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG AZEDO </t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>10.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>104403</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>104424</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE PEPSI COLA 2L</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>239315</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>248450</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>319396</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G  ANTIBACTERIANO LIMPEZA PROFUNDA</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>276292</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G FRUTAS VERMELHAS</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>276293</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G LAVANDA</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>276291</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G LIRIO SELVAGEM</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>276290</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G ROSA AVELUDADA</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>319398</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE CAPIM LIMAO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>319397</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE JASMIM ROXO</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>193867</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE HIDRATAÇÃO INTENENSA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>193868</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE LEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>193870</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE MENTOL</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>193869</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE MULTIAÇÃO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>193865</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE CONTROLE DE ODOR</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>193866</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85G SUAVE OLEO DE MACADAMIA</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>227599</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SABONTE ALBANY 85G SUAVE EXTRATO DE AVEIA</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>100705</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G TOMATE </t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>100693</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G OLEO </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>100373</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>106831</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TEMPERO SABORELE 930G COMPLETO</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>109729</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>WHISKY WHITE HORSE 1L</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>99.98999999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>239334</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>231292</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MIOLO DO ACEM KG</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>105469</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PALETA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>105452</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>PATINHO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>106053</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -1299,7 +1299,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L PINHO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
       <c r="E43" t="n">

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,181 +458,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>255232</v>
+        <v>104937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>298239</v>
+        <v>105023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.390000000000001</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100431</v>
+        <v>105010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 2L</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.39</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>133368</v>
+        <v>105001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>269680</v>
+        <v>104919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ DONA VAVA PCT 5KG TIPO 1 BRANCO </t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27.99</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>136523</v>
+        <v>104862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100020</v>
+        <v>104931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.99</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>186826</v>
+        <v>104855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO GALLO 360G CREAM CRACKER </t>
+          <t>LIMAO TAITI KG</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -642,733 +642,733 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>315855</v>
+        <v>104944</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BISCOITO RENATA 360G COCO</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.89</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>102085</v>
+        <v>104928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>114037</v>
+        <v>104947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>242311</v>
+        <v>104996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>287369</v>
+        <v>104992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>298701</v>
+        <v>104961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>184034</v>
+        <v>255232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>324556</v>
+        <v>298239</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>107928</v>
+        <v>107878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DENTAL COLGATE 180G MPA </t>
+          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.99</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>101063</v>
+        <v>116139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.69</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>208281</v>
+        <v>107395</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN </t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>208304</v>
+        <v>100038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML PROTECT UNISSEX </t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>208280</v>
+        <v>199440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN </t>
+          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.99</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>247502</v>
+        <v>113480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESINFETANTE +FAMILIA 5L LAVANDA </t>
+          <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>15.99</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>312369</v>
+        <v>132657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML ENERGY MEN </t>
+          <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>312371</v>
+        <v>107799</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO FLOR LAVANDA </t>
+          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>312370</v>
+        <v>261728</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE </t>
+          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>312366</v>
+        <v>199869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE PROTECT </t>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>312367</v>
+        <v>102085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FRUTAS VERMELHA </t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>312368</v>
+        <v>215568</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML POWER MEN </t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>298929</v>
+        <v>115855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN GIRL </t>
+          <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>298928</v>
+        <v>101137</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN SPORT </t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>298927</v>
+        <v>242311</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN BOY </t>
+          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>298933</v>
+        <v>252992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML INVISIBLE CARE </t>
+          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>298932</v>
+        <v>170451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN SPORT </t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>298931</v>
+        <v>247800</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML UNISSEX SPORT </t>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>298930</v>
+        <v>239446</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML SEM PERFUME </t>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>311881</v>
+        <v>242930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATAÇÃO INTENSA </t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.99</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>100423</v>
+        <v>309102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100419</v>
+        <v>107376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>220037</v>
+        <v>101066</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
+          <t>CREME DE LEITE ITALAC 200G</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>204461</v>
+        <v>112978</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1378,7 +1378,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>100420</v>
+        <v>148554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
+          <t>DESINFETANTE YPE BAK 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>100417</v>
+        <v>207588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1433,113 +1433,113 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>106661</v>
+        <v>207586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>312365</v>
+        <v>207584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FLOR DE ALGODAO WOMEN </t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>312364</v>
+        <v>207582</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML IMPACT MEN </t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>102287</v>
+        <v>256724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>273714</v>
+        <v>102282</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.289999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1548,90 +1548,90 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>155501</v>
+        <v>100780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.29</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>286381</v>
+        <v>155501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA DE 1KG PRETO</t>
+          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.69</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>163918</v>
+        <v>100027</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FEIJÃO KICALDO 1KG CARIOCA</t>
+          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.99</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>100119</v>
+        <v>279573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FLOCÃO DE MILHO SINHA 500G</t>
+          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2.79</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>113183</v>
+        <v>166152</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LEITE COND MARAJOARA 395G SEMIDESNATADO</t>
+          <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.79</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>170363</v>
+        <v>155080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEITE LEITBOM 1L INTEGRAL</t>
+          <t>LEITE CONDENSADO LEITBOM 395G</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1686,21 +1686,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>106922</v>
+        <v>170363</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>43.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1709,44 +1709,44 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>183340</v>
+        <v>307145</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LEITE ITALAC 1L UHT SEMI DESNATADO</t>
+          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6.69</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>131884</v>
+        <v>156422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>101728</v>
+        <v>108415</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12.69</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1778,21 +1778,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>169708</v>
+        <v>303196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASSA PARA TAPIOCA DO ZE 500G PRONTA </t>
+          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5.19</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>107640</v>
+        <v>101726</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MILHO VERDE QUERO LATA 170G</t>
+          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1824,113 +1824,113 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>321107</v>
+        <v>313828</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL </t>
+          <t>MASSA PARA TAPIOCA MATUTO 500G SEMI PRONTA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.29</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>106680</v>
+        <v>130920</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>145874</v>
+        <v>106680</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG AZEDO </t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>104403</v>
+        <v>316048</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
+          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>104424</v>
+        <v>128920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE PEPSI COLA 2L</t>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1939,682 +1939,429 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>104406</v>
+        <v>122984</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>REFRIGERANTE SPRITE 2L</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>10.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>239315</v>
+        <v>161871</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
+          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>248450</v>
+        <v>104406</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>319396</v>
+        <v>257710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G  ANTIBACTERIANO LIMPEZA PROFUNDA</t>
+          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.99</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>276292</v>
+        <v>228234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G FRUTAS VERMELHAS</t>
+          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>276293</v>
+        <v>100706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G LAVANDA</t>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>276291</v>
+        <v>259589</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G LIRIO SELVAGEM</t>
+          <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.99</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>276290</v>
+        <v>100876</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G ROSA AVELUDADA</t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>319398</v>
+        <v>106961</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE CAPIM LIMAO</t>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>319397</v>
+        <v>106960</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE JASMIM ROXO</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>193867</v>
+        <v>152232</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE HIDRATAÇÃO INTENENSA</t>
+          <t>BUCHO BOVINO KG</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>193868</v>
+        <v>105456</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE LEITE DE COCO</t>
+          <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>193870</v>
+        <v>105449</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE MENTOL</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>193869</v>
+        <v>105435</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE MULTIAÇÃO</t>
+          <t>COXAO MOLE KG</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>193865</v>
+        <v>173342</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE CONTROLE DE ODOR</t>
+          <t>MOCOTO BOVINO KG</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>193866</v>
+        <v>105475</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85G SUAVE OLEO DE MACADAMIA</t>
+          <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>227599</v>
+        <v>105433</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SABONTE ALBANY 85G SUAVE EXTRATO DE AVEIA</t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>100705</v>
+        <v>106052</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G TOMATE </t>
+          <t>PELE SUINA KG</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.39</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>100693</v>
+        <v>106034</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA GOMES DA COSTA 125G OLEO </t>
+          <t>SUAN SUINA KG</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>100373</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>106831</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>TEMPERO SABORELE 930G COMPLETO</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>109729</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>WHISKY WHITE HORSE 1L</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>99.98999999999999</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>239334</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>105458</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>107260</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>MAÇÃ DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>231292</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>MIOLO DO ACEM KG</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>105469</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>PALETA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>105452</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>PATINHO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>106053</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA CARRE KG</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>105062</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>18.99</v>
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,513 +458,513 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>104937</v>
+        <v>318330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105023</v>
+        <v>298239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.39</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105010</v>
+        <v>100426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>AGUA SANITARIA QBOA 1L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.59</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105001</v>
+        <v>112174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>ALCOOL START 70º 1L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>104919</v>
+        <v>116139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.29</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>104862</v>
+        <v>107395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>104931</v>
+        <v>269680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t xml:space="preserve">ARROZ DONA VAVA PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.890000000000001</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104855</v>
+        <v>100037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LIMAO TAITI KG</t>
+          <t>ARROZ PAINHO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.59</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>104944</v>
+        <v>225003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t xml:space="preserve">ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.89</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104928</v>
+        <v>186826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t xml:space="preserve">BISCOITO GALLO 360G CREAM CRACKER </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.99</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104947</v>
+        <v>315854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>BISCOITO RENATA 360G MAIZENA</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.69</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104996</v>
+        <v>102085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.39</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>104992</v>
+        <v>114037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>104961</v>
+        <v>287369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>255232</v>
+        <v>170451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>18.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>298239</v>
+        <v>168466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
+          <t xml:space="preserve">CERVEJA EISENBAHN LONG NECK 355ML PILSEN </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.49</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>107878</v>
+        <v>298701</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.89</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>116139</v>
+        <v>242930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>107395</v>
+        <v>309102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100038</v>
+        <v>107376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>199440</v>
+        <v>286362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+          <t>CERVEJA SPATEN LONG NECK 600ML PURO MALTE</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>29.39</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>113480</v>
+        <v>155079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
+          <t>CREME DE LEITE LEITBOM 200G</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>33.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -973,573 +973,573 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>132657</v>
+        <v>110330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.98999999999999</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>107799</v>
+        <v>247502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
+          <t xml:space="preserve">DESINFETANTE +FAMILIA 5L LAVANDA </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>261728</v>
+        <v>100423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>199869</v>
+        <v>100419</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102085</v>
+        <v>220037</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>215568</v>
+        <v>204461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>39.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>115855</v>
+        <v>100420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15.89</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>101137</v>
+        <v>100417</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>16.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>242311</v>
+        <v>106661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8.49</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>252992</v>
+        <v>253879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
+          <t>ENERGETICO BALY LATA 250ML MAÇÃ VERDE</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>170451</v>
+        <v>244425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>ENERGETICO BALY LATA 250ML FRUTAS TROPICAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>247800</v>
+        <v>244427</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t xml:space="preserve">ENERGETICO BALY LATA 250ML MELANCIA </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>239446</v>
+        <v>318892</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
+          <t>ENERGETICO BALY LATA 250ML ABACAXI  COM HORTELÃ</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.29</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>242930</v>
+        <v>244422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
+          <t>ENERGETICO BALY LATA 250ML COCO E ACAI</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>309102</v>
+        <v>312640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
+          <t>ENERGETICO BALY LATA 250ML COLA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.19</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>107376</v>
+        <v>303516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
+          <t>ENERGETICO BALY LATA 250ML FLYNOW SEM ACUCAR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>101066</v>
+        <v>312067</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CREME DE LEITE ITALAC 200G</t>
+          <t>ENERGETICO BALY LATA 250ML FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>112978</v>
+        <v>302658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500G</t>
+          <t>ENERGETICO BALY LATA 250ML MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>148554</v>
+        <v>302659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPE BAK 2L EUCALIPTO</t>
+          <t>ENERGETICO BALY LATA 250ML TANGERINA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>207588</v>
+        <v>312639</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>ENERGETICO BALY LATA 250ML TROPICAL ZERO AÇUCAR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>207586</v>
+        <v>303517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>ENERGETICO BALY LATA 250ML ZERO AÇUCAR</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>207584</v>
+        <v>100780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.69</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>207582</v>
+        <v>134629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.69</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>256724</v>
+        <v>163918</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>FEIJÃO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.69</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>102282</v>
+        <v>100119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t>FLOCÃO DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1548,21 +1548,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100780</v>
+        <v>170363</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>155501</v>
+        <v>106922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.19</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1594,44 +1594,44 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>100027</v>
+        <v>131884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8.289999999999999</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>279573</v>
+        <v>101728</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6.39</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>166152</v>
+        <v>302126</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
+          <t>MASSA PARA TAPIOCA DONA DE 1KG HIDRATADA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>155080</v>
+        <v>107640</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO LEITBOM 395G</t>
+          <t>MILHO VERDE QUERO LATA 170G</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.69</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1686,21 +1686,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>170363</v>
+        <v>101130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LEITE LEITBOM 1L INTEGRAL</t>
+          <t xml:space="preserve">MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7.69</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1709,44 +1709,44 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>307145</v>
+        <v>321107</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
+          <t xml:space="preserve">MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20.89</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>156422</v>
+        <v>106680</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.99</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1755,90 +1755,90 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>108415</v>
+        <v>144572</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
+          <t xml:space="preserve">POLVILHO LOPES 1KG DOCE </t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.89</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>303196</v>
+        <v>104404</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.39</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>101726</v>
+        <v>108686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8.99</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>313828</v>
+        <v>104406</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MASSA PARA TAPIOCA MATUTO 500G SEMI PRONTA</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1847,520 +1847,382 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>130920</v>
+        <v>239315</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t xml:space="preserve">BISCOITO RANCHEIRO 600G ROSQUINHA COCO </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.89</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>106680</v>
+        <v>286199</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
+          <t xml:space="preserve">SABÃO EM PO TIXAN YPE CAIXA 800G MACIEZ </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9.49</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>316048</v>
+        <v>261083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
+          <t>SABÃO EM PO TIXAN YPE CAIXA 800G PRIMAVERA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>128920</v>
+        <v>100373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>122984</v>
+        <v>100876</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>REFRIGERANTE SPRITE 2L</t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.69</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>161871</v>
+        <v>109729</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
+          <t>WHISKY WHITE HORSE 1L</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>7.99</v>
+        <v>110.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>104406</v>
+        <v>105460</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>BISTECA BOVINA KG PALETA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>257710</v>
+        <v>105459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
+          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>12.79</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>228234</v>
+        <v>105451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+          <t>CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>15.89</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100706</v>
+        <v>105471</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t>COSTELA BOVINA KG</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.69</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>259589</v>
+        <v>105469</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
+          <t>PALETA BOVINA KG</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10.59</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>100876</v>
+        <v>106008</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>14.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>106961</v>
+        <v>106053</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+          <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>106960</v>
+        <v>105062</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>152232</v>
+        <v>105433</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>13.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>105456</v>
+        <v>106054</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>LOMBO SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>105449</v>
+        <v>106052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>PELE SUINA KG</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>105435</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>COXAO MOLE KG</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>173342</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>MOCOTO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>105475</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>MUSCULO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>105433</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>COSTELA SUINA KG</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>106052</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>106034</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SUAN SUINA KG</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.59</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.59</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.89</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="11">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="13">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -904,15 +904,15 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100038</v>
+        <v>225670</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>ARROZ BENTO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="22">
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>199440</v>
+        <v>100038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>29.39</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="23">
@@ -950,15 +950,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>113480</v>
+        <v>199440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
+          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>33.49</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="24">
@@ -969,19 +969,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>132657</v>
+        <v>113480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
+          <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.98999999999999</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="25">
@@ -992,19 +992,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>107799</v>
+        <v>132657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
+          <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1015,19 +1015,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>261728</v>
+        <v>107799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
+          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.69</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="27">
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>199869</v>
+        <v>261728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
+          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7.69</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="28">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102085</v>
+        <v>199869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="29">
@@ -1088,15 +1088,15 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>215568</v>
+        <v>102085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>39.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="30">
@@ -1107,19 +1107,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>115855</v>
+        <v>215568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>15.89</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="31">
@@ -1134,15 +1134,15 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>101137</v>
+        <v>115855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>16.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="32">
@@ -1157,15 +1157,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>242311</v>
+        <v>101137</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8.49</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="33">
@@ -1180,15 +1180,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>252992</v>
+        <v>242311</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
+          <t xml:space="preserve">CATCHUP ARISCO 370G TRADICIONAL </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="34">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>170451</v>
+        <v>252992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.89</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>247800</v>
+        <v>170451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.69</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="36">
@@ -1245,19 +1245,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>239446</v>
+        <v>247800</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.29</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="37">
@@ -1268,19 +1268,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>242930</v>
+        <v>239446</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.89</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="38">
@@ -1291,19 +1291,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>309102</v>
+        <v>242930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.19</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="39">
@@ -1318,15 +1318,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>107376</v>
+        <v>309102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
+          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.99</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="40">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>101066</v>
+        <v>107376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CREME DE LEITE ITALAC 200G</t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="41">
@@ -1364,15 +1364,15 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>112978</v>
+        <v>101066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500G</t>
+          <t>CREME DE LEITE ITALAC 200G</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="42">
@@ -1383,19 +1383,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>148554</v>
+        <v>112978</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPE BAK 2L EUCALIPTO</t>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43">
@@ -1410,15 +1410,15 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>207588</v>
+        <v>148554</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>DESINFETANTE YPE BAK 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="44">
@@ -1521,19 +1521,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>102282</v>
+        <v>207588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="49">
@@ -1544,19 +1544,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100780</v>
+        <v>102282</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="50">
@@ -1571,15 +1571,15 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>155501</v>
+        <v>100780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.19</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="51">
@@ -1594,15 +1594,15 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>100027</v>
+        <v>155501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
+          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8.289999999999999</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="52">
@@ -1613,19 +1613,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>279573</v>
+        <v>100027</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6.39</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -1636,19 +1636,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>166152</v>
+        <v>279573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
+          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3.29</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="54">
@@ -1663,15 +1663,15 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>155080</v>
+        <v>166152</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO LEITBOM 395G</t>
+          <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.69</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="55">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>170363</v>
+        <v>155080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LEITE LEITBOM 1L INTEGRAL</t>
+          <t>LEITE CONDENSADO LEITBOM 395G</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1709,15 +1709,15 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>307145</v>
+        <v>170363</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20.89</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="57">
@@ -1728,19 +1728,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>156422</v>
+        <v>307145</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
+          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.99</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="58">
@@ -1751,19 +1751,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>108415</v>
+        <v>156422</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
+          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="59">
@@ -1778,15 +1778,15 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>303196</v>
+        <v>108415</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
+          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.39</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="60">
@@ -1801,15 +1801,15 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>101726</v>
+        <v>303196</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="61">
@@ -1824,15 +1824,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>313828</v>
+        <v>101726</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MASSA PARA TAPIOCA MATUTO 500G SEMI PRONTA</t>
+          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="62">
@@ -1847,15 +1847,15 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>130920</v>
+        <v>313828</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t>MASSA PARA TAPIOCA MATUTO 500G SEMI PRONTA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="63">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>106680</v>
+        <v>130920</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="64">
@@ -1889,19 +1889,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>316048</v>
+        <v>106680</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="65">
@@ -1912,19 +1912,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>128920</v>
+        <v>316048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="66">
@@ -1935,19 +1935,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>122984</v>
+        <v>128920</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>REFRIGERANTE SPRITE 2L</t>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="67">
@@ -1962,15 +1962,15 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>161871</v>
+        <v>122984</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
+          <t>REFRIGERANTE SPRITE 2L</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>7.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="68">
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>104406</v>
+        <v>161871</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="69">
@@ -2004,19 +2004,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>257710</v>
+        <v>104406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>12.79</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="70">
@@ -2031,15 +2031,15 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>228234</v>
+        <v>257710</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>15.89</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="71">
@@ -2050,19 +2050,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100706</v>
+        <v>228234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.69</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="72">
@@ -2073,19 +2073,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>259589</v>
+        <v>100706</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10.59</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="73">
@@ -2096,19 +2096,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>100876</v>
+        <v>259589</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
+          <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>14.99</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="74">
@@ -2123,15 +2123,15 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>106961</v>
+        <v>100876</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="75">
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>106960</v>
+        <v>106961</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2160,24 +2160,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>152232</v>
+        <v>106960</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>13.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="77">
@@ -2192,15 +2192,15 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>105456</v>
+        <v>152232</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>BUCHO BOVINO KG</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="78">
@@ -2215,15 +2215,15 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>105449</v>
+        <v>105456</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>33.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="79">
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>105435</v>
+        <v>105449</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>36.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="80">
@@ -2261,15 +2261,15 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>173342</v>
+        <v>105435</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MOCOTO BOVINO KG</t>
+          <t>COXAO MOLE KG</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="81">
@@ -2284,15 +2284,15 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>105475</v>
+        <v>173342</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t>MOCOTO BOVINO KG</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>21.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="82">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>105433</v>
+        <v>105475</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>23.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="83">
@@ -2330,15 +2330,15 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>106052</v>
+        <v>105433</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>12.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="84">
@@ -2353,14 +2353,37 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>106052</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PELE SUINA KG</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
         <v>106034</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="E85" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,253 +458,1863 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105460</v>
+        <v>255232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105459</v>
+        <v>298239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105451</v>
+        <v>100431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105471</v>
+        <v>181416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t>AMACINATE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105469</v>
+        <v>179914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PALETA BOVINA KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>106008</v>
+        <v>234617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INGREDIENTES PARA FEIJOADA KG</t>
+          <t xml:space="preserve">BISCOITO ESTRELA 350G CREAM CRACKER </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.99</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>106053</v>
+        <v>199869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BISTECA SUINA CARRE KG</t>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105062</v>
+        <v>102085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>105433</v>
+        <v>101137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>23.99</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>106054</v>
+        <v>287369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LOMBO SUINO FRESCO KG</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>170451</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>239446</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>184034</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN LONG NECK 250ML LAGER</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>101066</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE ITALAC 200G</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>123791</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>123792</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>123793</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>123795</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>123796</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>123797</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>256724</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>207588</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>207586</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>207584</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>207582</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>102287</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>100780</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>134629</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>268021</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FARINHA DE MANDIOCA XINGU 1KG FINA AMARELA</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100024</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>167686</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>140665</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEIJAO KICALDO 1KG RETO </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>100120</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>108434</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>174382</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE EM PO ITALAC 1KG  INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>142446</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE ITALAC 1L INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>183340</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LEITE ITALAC 1L UHT SEMI DESNATADO</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>125011</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACARRÃO CRISTAL 500G PARAFUSO COM OVOS </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>131884</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>101728</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>169708</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASSA PARA TAPIOCA DO ZE 500G PRONTA </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>130920</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>168910</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MISTURA PARA BOLO ITALAC 400G CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>106680</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OLEO DE SOJA SOYA 900ML</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>236651</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>128920</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>104403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>248450</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>100706</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 SUCO</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>102237</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>106831</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TEMPERO SABORELE 930G COMPLETO</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>106961</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>106960</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>102077</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>179.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>105842</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ASA DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>227503</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>104602</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>105838</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>105840</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>14.59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>306504</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FIGADO DE FRANGO PERDIGAO KG</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>109597</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FILE DE PEITO DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>108788</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>228289</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FRANGO INTEIRO SADIA KG TEMPERADO SEM MIUDOS</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>185934</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GALINHA NOROESTE CONGELADA KG</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>228422</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>309350</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MASSA DE PASTEL JK 1KG</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>309331</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASSA DE PASTEL JK 500G DISCAO </t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>309332</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASSA DE PASTEL JK 500G ROLO </t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>108773</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>261357</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>130293</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PIZZA SEARA 460G FRANGO COM CATUPIRY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>108771</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>157014</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>105456</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>105468</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>106052</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="C81" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,21 +467,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>255232</v>
+        <v>318330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.59</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.39</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -582,67 +582,67 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>234617</v>
+        <v>123206</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO ESTRELA 350G CREAM CRACKER </t>
+          <t xml:space="preserve">AZEITONAS LA VIOLETERA SACHÊ 160G FATIADA </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.39</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>199869</v>
+        <v>107799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
+          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102085</v>
+        <v>261728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,241 +651,241 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>101137</v>
+        <v>315854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>BISCOITO RENATA 360G MAIZENA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>16.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>287369</v>
+        <v>199869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+          <t xml:space="preserve">BISCOITO ADORALLE 600G ROSQUINHA DE COCO </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.49</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>170451</v>
+        <v>102085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.79</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>239446</v>
+        <v>101137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.19</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184034</v>
+        <v>168712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN LONG NECK 250ML LAGER</t>
+          <t>CERVEJA ANTARCTICA 15 X 269ML PILSEN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.99</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>101066</v>
+        <v>170451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CREME DE LEITE ITALAC 200G</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>123791</v>
+        <v>247800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML LARGER</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>123792</v>
+        <v>239446</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>123793</v>
+        <v>267604</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>123795</v>
+        <v>242930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>123796</v>
+        <v>157496</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+          <t>CERVEJA HEINEKEN 600ML</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -895,53 +895,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>123797</v>
+        <v>101066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L PINHO</t>
+          <t>CREME DE LEITE ITALAC 200G</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>256724</v>
+        <v>110330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -950,21 +950,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>207588</v>
+        <v>259583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2L ERVA DOCE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>207586</v>
+        <v>207624</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS FLORAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>207584</v>
+        <v>207626</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS JASMIN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1019,195 +1019,195 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>207582</v>
+        <v>207628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS LAVANDA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>102287</v>
+        <v>207630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS LIMAO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.99</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>100780</v>
+        <v>119826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>134629</v>
+        <v>111567</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>268021</v>
+        <v>110352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA XINGU 1KG FINA AMARELA</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100024</v>
+        <v>110353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.89</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>167686</v>
+        <v>252617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>140665</v>
+        <v>106663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJAO KICALDO 1KG RETO </t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100120</v>
+        <v>112163</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MARINE</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1217,283 +1217,283 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>108434</v>
+        <v>244424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>174382</v>
+        <v>253877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO ITALAC 1KG  INTEGRAL </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>38.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>142446</v>
+        <v>253878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE ITALAC 1L INTEGRAL </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>183340</v>
+        <v>253880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LEITE ITALAC 1L UHT SEMI DESNATADO</t>
+          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>125011</v>
+        <v>244426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRÃO CRISTAL 500G PARAFUSO COM OVOS </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>131884</v>
+        <v>305261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+          <t>ENERGETICO BALY 2L ABACAXI COM HORTELA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.39</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>101728</v>
+        <v>320467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>169708</v>
+        <v>302661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASSA PARA TAPIOCA DO ZE 500G PRONTA </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L MORANGO E PESSEGO </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>130920</v>
+        <v>302660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L TANGERINA </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>168910</v>
+        <v>102287</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MISTURA PARA BOLO ITALAC 400G CHOCOLATE</t>
+          <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>106680</v>
+        <v>100780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>9.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>236651</v>
+        <v>273006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
+          <t>FARINHA LACTEA NESTLE 160G ORIGINAL</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1502,90 +1502,90 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>128920</v>
+        <v>107361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+          <t xml:space="preserve">FARINHA DE TRIGO DONA BENTA 1KG COM FERMENTO </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>104403</v>
+        <v>100024</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>104406</v>
+        <v>100119</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>FLOCÃO DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10.49</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>248450</v>
+        <v>108434</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>20.99</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1594,44 +1594,44 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>100706</v>
+        <v>101113</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t xml:space="preserve">LEITE PIRACANJUBA 1L INTEGRAL </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 SUCO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>102237</v>
+        <v>106922</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>27.99</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>106831</v>
+        <v>108415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELE 930G COMPLETO</t>
+          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>106961</v>
+        <v>303196</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
+          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1686,126 +1686,126 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>106960</v>
+        <v>101728</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>102077</v>
+        <v>169708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
+          <t xml:space="preserve">MASSA PARA TAPIOCA DO ZE 500G PRONTA </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>179.99</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>105842</v>
+        <v>130920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>14.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>227503</v>
+        <v>106680</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>104602</v>
+        <v>236651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+          <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>15.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>105838</v>
+        <v>145874</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG AZEDO </t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1815,112 +1815,112 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>105840</v>
+        <v>128920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>14.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>306504</v>
+        <v>104404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FIGADO DE FRANGO PERDIGAO KG</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5.99</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>109597</v>
+        <v>104403</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20.99</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>108788</v>
+        <v>104424</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+          <t>REFRIGERANTE PEPSI COLA 2L</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>19.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>228289</v>
+        <v>104406</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FRANGO INTEIRO SADIA KG TEMPERADO SEM MIUDOS</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -1930,53 +1930,53 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>185934</v>
+        <v>326954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GALINHA NOROESTE CONGELADA KG</t>
+          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.19</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>228422</v>
+        <v>228234</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>18.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1985,44 +1985,44 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>309350</v>
+        <v>100706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MASSA DE PASTEL JK 1KG</t>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 SUCO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>309331</v>
+        <v>264452</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASSA DE PASTEL JK 500G DISCAO </t>
+          <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2031,291 +2031,636 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>309332</v>
+        <v>100876</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASSA DE PASTEL JK 500G ROLO </t>
+          <t xml:space="preserve">TEMPERO ARISCO COMPLETO 1KG PIMENTA </t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>108773</v>
+        <v>106961</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+          <t xml:space="preserve">VINAGRE CASTELO 750ML ALCOOL </t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>17.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>261357</v>
+        <v>106960</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>18.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>130293</v>
+        <v>102087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PIZZA SEARA 460G FRANGO COM CATUPIRY</t>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21.99</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>108771</v>
+        <v>110373</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
+          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>17.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>157014</v>
+        <v>102077</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
+          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>13.99</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>105456</v>
+        <v>104937</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>26.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>105468</v>
+        <v>105023</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>17.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>105458</v>
+        <v>105010</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>18.99</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>105449</v>
+        <v>105001</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>32.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>105435</v>
+        <v>104919</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>33.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>105062</v>
+        <v>104862</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>18.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>104931</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>104855</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>104944</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MACA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>104928</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MANGA PALMER KG</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>104996</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>104992</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>104961</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>239334</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>105463</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CORAÇÃO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>106034</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SUAN SUINA KG</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>13.99</v>
+      <c r="C96" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>105433</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>COSTELA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,553 +458,737 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>298239</v>
+        <v>230698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
+          <t>GIN TANQUERAI TEN 750ML</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.69</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100038</v>
+        <v>286589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100031</v>
+        <v>287184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>326645</v>
+        <v>286326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ PCT 5KG TIPO 1 BRANCO</t>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>167128</v>
+        <v>287177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>105460</v>
+        <v>215568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105461</v>
+        <v>157068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BISTECA DO CONTRA FILE KG</t>
+          <t>CERVEJA BRAHMA DUPLO MALTE 12 X 350ML</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105451</v>
+        <v>265727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>CERVEJA HEINEKEN 8 X 269ML</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>105463</v>
+        <v>298123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO KG</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>105471</v>
+        <v>107376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105449</v>
+        <v>295198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t xml:space="preserve">CHOPP DE VINHO STEMPEL 600ML RED </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106065</v>
+        <v>102282</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FIGADO BOVINO KG</t>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11.99</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105838</v>
+        <v>273004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t xml:space="preserve">ENERGETICO ENGOV UP 269ML MELANCIA </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>105840</v>
+        <v>273000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>141831</v>
+        <v>273005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FILÉ DE PANGA KG</t>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>203263</v>
+        <v>324170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA KG</t>
+          <t>BEBIDA ENGOV AFTER 250ML PINK LEMONADE</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>109597</v>
+        <v>286271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
+          <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>19.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105853</v>
+        <v>139964</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
+          <t xml:space="preserve">VINHO PERGOLA 1L TINTO SUAVE </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10.89</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>305039</v>
+        <v>102087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>123758</v>
+        <v>110373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LINGUICA FRIMESA KG TOSCANA MISTA</t>
+          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>22.99</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>189031</v>
+        <v>137381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LINGUICA FRICO MISTA KG</t>
+          <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17.99</v>
+        <v>128.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>105062</v>
+        <v>248750</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18.99</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>106054</v>
+        <v>102077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOMBO SUINO FRESCO KG</t>
+          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>18.99</v>
+        <v>195.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>105450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ALCATRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>105451</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>261519</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PICANHA BOVINA KG FATIADA</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>258810</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PANCETA SUINA KG</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>18.99</v>
+      <c r="C33" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="84">
   <si>
     <t>Promoção</t>
   </si>
@@ -31,13 +31,19 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SEGUNDA - OFERTAS 12/05/2025</t>
-  </si>
-  <si>
-    <t>SEGUNDA - COROCOCO 12/05/25</t>
-  </si>
-  <si>
-    <t>SEGUNDA - AÇOUGUE 12/05/25</t>
+    <t>TERÇA - AÇOUGUE 13/05/25</t>
+  </si>
+  <si>
+    <t>TERCA - OFERTAS 13/05/2025</t>
+  </si>
+  <si>
+    <t>TERÇA - PERECIVEIS 13/05/25</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - BOVINO</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - EMBUTIDO</t>
   </si>
   <si>
     <t>#02 MERCEARIA</t>
@@ -55,10 +61,13 @@
     <t>#05 BEBIDA - DESTILADOS</t>
   </si>
   <si>
+    <t>#05 BEBIDA - CERVEJA CX</t>
+  </si>
+  <si>
     <t>#05 BEBIDA - CERVEJA</t>
   </si>
   <si>
-    <t>#05 BEBIDA - CERVEJA CX</t>
+    <t>#05 BEBIDA - #00 ENERGETICO</t>
   </si>
   <si>
     <t>#04 HIGIENE PESSOAL</t>
@@ -67,19 +76,25 @@
     <t>#05 BEBIDA - #00 REFRIGERANTES</t>
   </si>
   <si>
-    <t>#05 BEBIDA - #00 SUCO</t>
-  </si>
-  <si>
     <t>#06 AÇOUGUE - AVE</t>
   </si>
   <si>
-    <t>#06 AÇOUGUE - EMBUTIDO</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - BOVINO</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - SUINO</t>
+    <t>CARNE DE SOL KG SEGUNDA</t>
+  </si>
+  <si>
+    <t>CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>MUSCULO BOVINO KG</t>
+  </si>
+  <si>
+    <t>LINGUICA BOVINA CASEIRA KG</t>
   </si>
   <si>
     <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
@@ -88,235 +103,169 @@
     <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
   </si>
   <si>
-    <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
-  </si>
-  <si>
-    <t>ALCOOL START 70º 1L</t>
+    <t>AGUA SANITARIA QBOA 1L</t>
   </si>
   <si>
     <t>AMACIANTE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
   </si>
   <si>
-    <t>AMACIANTE DE ROUPAS YPE 2L INTENSO PROMOCIONAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARROZ DONA VAVA PCT 5KG TIPO 1 BRANCO </t>
-  </si>
-  <si>
-    <t>ARROZ RACHA PANELA PCT 5KG TIPO 1 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
-  </si>
-  <si>
-    <t>ARROZ SEU ARROZ PCT 5KG TIPO 1 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZEITE DE OLIVA GALLO VIDRO 500ML EXTRA VIRGEM </t>
+    <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+  </si>
+  <si>
+    <t>ARROZ TIO URBANO PCT 5KG TIPO 1 BRANCO</t>
   </si>
   <si>
     <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
   </si>
   <si>
-    <t>BISCOITO RENATA 360G COCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BISCOITO SULLPER 600G ROSQUINHA COCO </t>
+    <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOMBOM GAROTO CAIXA 250G SORTIDO </t>
   </si>
   <si>
     <t>CACHACA 51 965ML</t>
   </si>
   <si>
-    <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
-  </si>
-  <si>
-    <t>CERVEJA ANTARCTICA 269ML SUBZERO</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER 15 X 269ML</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN 330ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
-  </si>
-  <si>
-    <t>CREME DE LEITE LEITBOM 200G</t>
-  </si>
-  <si>
-    <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
-  </si>
-  <si>
-    <t>DESINFETANTE +FAMILIA 2L PINHO</t>
-  </si>
-  <si>
-    <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
-  </si>
-  <si>
-    <t>EXTRATO DE TOMATE OLE COPO 260G</t>
-  </si>
-  <si>
-    <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
-  </si>
-  <si>
-    <t>FEIJAO DA CASA 1KG CARIOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEIJAO KICALDO 1KG RETO </t>
-  </si>
-  <si>
-    <t>FLOCÃO DE MILHO AMAFIL 500G</t>
-  </si>
-  <si>
-    <t>KETCHUP QUERO 400G TRADICIONAL</t>
-  </si>
-  <si>
-    <t>LEITE CONDENSADO TRIANGULO 395G TP SEMIDESNATADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEITE EM PO ITALAC 1KG  INTEGRAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
-  </si>
-  <si>
-    <t>MAIONESE ARISCO 500G TRADICIONAL</t>
-  </si>
-  <si>
-    <t>MILHO VERDE SOFRUTA LATA 170G</t>
-  </si>
-  <si>
-    <t>MISTURA PARA BOLO ITALAC 400G CHOCOLATE</t>
-  </si>
-  <si>
-    <t>MOLHO DE TOMATE SABORELLE 300G TRADICIONAL</t>
-  </si>
-  <si>
-    <t>OLEO DE SOJA CONCORDIA 900ML</t>
+    <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+  </si>
+  <si>
+    <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+  </si>
+  <si>
+    <t>CERVEJA BUDWEISER LONG NECK 330ML LARGER</t>
+  </si>
+  <si>
+    <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 350ML SLEEK</t>
+  </si>
+  <si>
+    <t>CORONA EXTRA 330ML LONG NECK</t>
+  </si>
+  <si>
+    <t>CREME DE LEITE ITALAC 200G</t>
+  </si>
+  <si>
+    <t>CUSCUZ DE MILHO SINHA 500G</t>
+  </si>
+  <si>
+    <t>DESINFETANTE YPE BAK 2L EUCALIPTO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENERGETICO ENGOV UP 269ML MELANCIA </t>
+  </si>
+  <si>
+    <t>ENERGETICO EXTRA POWER 270ML</t>
+  </si>
+  <si>
+    <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+  </si>
+  <si>
+    <t>FEIJÃO KICALDO 1KG CARIOCA</t>
+  </si>
+  <si>
+    <t>FLOCÃO DE MILHO SINHA 500G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEITE ITALAC 1L INTEGRAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACARRÃO PAULISTA 500G SEMOLA ESPAGUETE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIONESE HELLMANNS 500G TRADICIONAL </t>
+  </si>
+  <si>
+    <t>MAIONESE QUERO SACHE 200G</t>
+  </si>
+  <si>
+    <t>MILHO VERDE BONARE LATA 170G</t>
+  </si>
+  <si>
+    <t>OLEO DE SOJA SOYA 900ML</t>
   </si>
   <si>
     <t>PAPEL HIGIENICO NOBLE 12 X 20M</t>
   </si>
   <si>
-    <t xml:space="preserve">POLVILHO MATUTO 1KG AZEDO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+    <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
+  </si>
+  <si>
+    <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
   </si>
   <si>
     <t>REFRIGERANTE COCA COLA 2L</t>
   </si>
   <si>
-    <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SABÃO EM PO TIXAN YPE CAIXA 800G MACIEZ </t>
-  </si>
-  <si>
-    <t>SABÃO EM PO TIXAN YPE CAIXA 800G PRIMAVERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
-  </si>
-  <si>
-    <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
-  </si>
-  <si>
-    <t>TEMPERO SABORELE 930G COMPLETO</t>
-  </si>
-  <si>
-    <t>VINAGRE SABORELLE 750ML COMPOSTO BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
-  </si>
-  <si>
-    <t>ASA DE FRANGO KG</t>
-  </si>
-  <si>
-    <t>BATATA SADIA PCT 400G CONGELADA PRE-FRITA PALITO</t>
-  </si>
-  <si>
-    <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
-  </si>
-  <si>
-    <t>COXA DE FRANGO SADIA PCT 1KG</t>
-  </si>
-  <si>
-    <t>COXA COM SOBRECOXA DE FRANGO KG</t>
-  </si>
-  <si>
-    <t>COXINHA DA ASA DE FRANGO KG</t>
-  </si>
-  <si>
-    <t>FIGADO DE FRANGO PERDIGAO KG</t>
-  </si>
-  <si>
-    <t>FILE DE PEITO DE FRANGO KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+    <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
+  </si>
+  <si>
+    <t>SODA CAUSTICA SOL 1KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPERO ARISCO 1KG COMPLETO COM PIMENTA </t>
+  </si>
+  <si>
+    <t>WHISKY WHITE HORSE 1L</t>
+  </si>
+  <si>
+    <t>COXINHA DA ASA SADIA PCT 1KG DRUMETE</t>
+  </si>
+  <si>
+    <t>FILE DE COXA E SOBRE COXA SEARA BDJ 1KG</t>
+  </si>
+  <si>
+    <t>FILEZINHO DE PEITO SEARA BDJ 1KG SASSAMI</t>
   </si>
   <si>
     <t>FRANGO AMERICANO KG</t>
   </si>
   <si>
-    <t>GALINHA NOROESTE CONGELADA KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
-  </si>
-  <si>
-    <t>MASSA DE PASTEL JK 1KG</t>
-  </si>
-  <si>
-    <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
-  </si>
-  <si>
-    <t>MORTADELA SADIA DE FRANGO KG</t>
-  </si>
-  <si>
-    <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
-  </si>
-  <si>
-    <t>PIZZA SEARA 460G FRANGO COM CATUPIRY</t>
-  </si>
-  <si>
-    <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
-  </si>
-  <si>
-    <t>BISTECA BOVINA KG PALETA</t>
-  </si>
-  <si>
-    <t>ACEM BOVINO KG</t>
-  </si>
-  <si>
-    <t>BISTECA DA MAÇÃ DO PEITO KG</t>
-  </si>
-  <si>
-    <t>CAPA DO CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>CHAMBARI KG</t>
-  </si>
-  <si>
-    <t>COXÃO DURO KG</t>
-  </si>
-  <si>
-    <t>COXAO MOLE KG</t>
-  </si>
-  <si>
-    <t>BISTECA SUINA DO PERNIL KG</t>
-  </si>
-  <si>
-    <t>SUAN SUINA KG</t>
+    <t>LINGUICA FRICO MISTA KG</t>
+  </si>
+  <si>
+    <t>PAO DE QUEIJO VITORIA 300G TRADICIONAL ESPECIAL</t>
+  </si>
+  <si>
+    <t>PAO DE QUEIJO BRASIL 300G PREMIUM TRADICIONAL</t>
   </si>
 </sst>
 </file>
@@ -674,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -702,13 +651,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>255232</v>
+        <v>105456</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>18.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -716,16 +665,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>298239</v>
+        <v>105468</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>8.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -733,16 +682,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>107878</v>
+        <v>105471</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>4.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -750,16 +699,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>112174</v>
+        <v>107260</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>11.39</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -767,16 +716,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>181416</v>
+        <v>105475</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>11.69</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -784,1325 +733,985 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>179914</v>
+        <v>305039</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>11.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>269680</v>
+        <v>255232</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>23.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9">
-        <v>199439</v>
+        <v>298239</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>25.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>100031</v>
+        <v>100426</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>27.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>326645</v>
+        <v>181416</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>132657</v>
+        <v>136523</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>66.98999999999999</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>250013</v>
+        <v>113480</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13">
-        <v>5.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>315855</v>
+        <v>250013</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14">
-        <v>6.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>286746</v>
+        <v>286197</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>102085</v>
+        <v>239682</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>12.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C17">
-        <v>115855</v>
+        <v>102085</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>239441</v>
+        <v>101137</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>2.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>298701</v>
+        <v>287369</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>313599</v>
+        <v>170451</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>3.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>242930</v>
+        <v>247800</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>107376</v>
+        <v>267604</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>155079</v>
+        <v>303282</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E23">
-        <v>3.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>110330</v>
+        <v>220499</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>2.19</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>100315</v>
+        <v>101066</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25">
-        <v>6.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>256724</v>
+        <v>112978</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>207588</v>
+        <v>148554</v>
       </c>
       <c r="D27" t="s">
         <v>46</v>
       </c>
       <c r="E27">
-        <v>1.79</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C28">
-        <v>207586</v>
+        <v>100423</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>207584</v>
+        <v>100419</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>207582</v>
+        <v>220037</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E30">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>118822</v>
+        <v>204461</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E31">
-        <v>4.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>100024</v>
+        <v>100420</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E32">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>116507</v>
+        <v>100417</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E33">
-        <v>5.39</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>140665</v>
+        <v>106661</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E34">
-        <v>8.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C35">
-        <v>255841</v>
+        <v>273004</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E35">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>100785</v>
+        <v>102287</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E36">
-        <v>7.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>220451</v>
+        <v>273714</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E37">
-        <v>6.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>174382</v>
+        <v>134629</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E38">
-        <v>36.99</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>131884</v>
+        <v>163918</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E39">
-        <v>3.39</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>101726</v>
+        <v>100119</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E40">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>234316</v>
+        <v>108434</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E41">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C42">
-        <v>168910</v>
+        <v>142446</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E42">
-        <v>4.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>287073</v>
+        <v>307145</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E43">
-        <v>2.19</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>167128</v>
+        <v>100642</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E44">
-        <v>8.789999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C45">
-        <v>236651</v>
+        <v>101728</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E45">
-        <v>18.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>145874</v>
+        <v>115724</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E46">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>104404</v>
+        <v>234626</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E47">
-        <v>9.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C48">
-        <v>104406</v>
+        <v>106680</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E48">
-        <v>10.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C49">
-        <v>286271</v>
+        <v>236651</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E49">
-        <v>7.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C50">
-        <v>257710</v>
+        <v>104403</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E50">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C51">
-        <v>286199</v>
+        <v>104410</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E51">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C52">
-        <v>261083</v>
+        <v>104406</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E52">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C53">
-        <v>100706</v>
+        <v>248450</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E53">
-        <v>5.69</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>102237</v>
+        <v>100373</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E54">
-        <v>28.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C55">
-        <v>106831</v>
+        <v>259589</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E55">
-        <v>11.69</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>137423</v>
+        <v>100876</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E56">
-        <v>4.29</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C57">
-        <v>102077</v>
+        <v>109729</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E57">
-        <v>195.99</v>
+        <v>110.99</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C58">
-        <v>105842</v>
+        <v>108785</v>
       </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E58">
-        <v>13.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C59">
-        <v>227503</v>
+        <v>299338</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E59">
-        <v>8.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60">
-        <v>119923</v>
+        <v>291440</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E60">
-        <v>32.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C61">
-        <v>104602</v>
+        <v>119927</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E61">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C62">
-        <v>105838</v>
+        <v>189031</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E62">
-        <v>11.69</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>105840</v>
+        <v>228484</v>
       </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E63">
-        <v>14.39</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C64">
-        <v>306504</v>
+        <v>320181</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E64">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65">
-        <v>109597</v>
-      </c>
-      <c r="D65" t="s">
-        <v>81</v>
-      </c>
-      <c r="E65">
-        <v>19.89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66">
-        <v>108788</v>
-      </c>
-      <c r="D66" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67">
-        <v>119927</v>
-      </c>
-      <c r="D67" t="s">
-        <v>83</v>
-      </c>
-      <c r="E67">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" t="s">
-        <v>18</v>
-      </c>
-      <c r="C68">
-        <v>185934</v>
-      </c>
-      <c r="D68" t="s">
-        <v>84</v>
-      </c>
-      <c r="E68">
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69">
-        <v>228422</v>
-      </c>
-      <c r="D69" t="s">
-        <v>85</v>
-      </c>
-      <c r="E69">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70">
-        <v>309350</v>
-      </c>
-      <c r="D70" t="s">
-        <v>86</v>
-      </c>
-      <c r="E70">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71">
-        <v>108773</v>
-      </c>
-      <c r="D71" t="s">
-        <v>87</v>
-      </c>
-      <c r="E71">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72">
-        <v>116251</v>
-      </c>
-      <c r="D72" t="s">
-        <v>88</v>
-      </c>
-      <c r="E72">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73">
-        <v>261357</v>
-      </c>
-      <c r="D73" t="s">
-        <v>89</v>
-      </c>
-      <c r="E73">
         <v>16.99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74">
-        <v>130293</v>
-      </c>
-      <c r="D74" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" t="s">
-        <v>18</v>
-      </c>
-      <c r="C75">
-        <v>108771</v>
-      </c>
-      <c r="D75" t="s">
-        <v>91</v>
-      </c>
-      <c r="E75">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76">
-        <v>105460</v>
-      </c>
-      <c r="D76" t="s">
-        <v>92</v>
-      </c>
-      <c r="E76">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77">
-        <v>105470</v>
-      </c>
-      <c r="D77" t="s">
-        <v>93</v>
-      </c>
-      <c r="E77">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78">
-        <v>105459</v>
-      </c>
-      <c r="D78" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79">
-        <v>239334</v>
-      </c>
-      <c r="D79" t="s">
-        <v>95</v>
-      </c>
-      <c r="E79">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80">
-        <v>105458</v>
-      </c>
-      <c r="D80" t="s">
-        <v>96</v>
-      </c>
-      <c r="E80">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81">
-        <v>105449</v>
-      </c>
-      <c r="D81" t="s">
-        <v>97</v>
-      </c>
-      <c r="E81">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82">
-        <v>105435</v>
-      </c>
-      <c r="D82" t="s">
-        <v>98</v>
-      </c>
-      <c r="E82">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83">
-        <v>105062</v>
-      </c>
-      <c r="D83" t="s">
-        <v>99</v>
-      </c>
-      <c r="E83">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84">
-        <v>106034</v>
-      </c>
-      <c r="D84" t="s">
-        <v>100</v>
-      </c>
-      <c r="E84">
-        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,162 +458,1082 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105460</v>
+        <v>311307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
+          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105456</v>
+        <v>303488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27.99</v>
+        <v>118.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105458</v>
+        <v>323495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>CAMARÃO COSTA SUL 300G COZIDO DECASCADO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105449</v>
+        <v>262170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105487</v>
+        <v>164651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUPIM BOVINO KG </t>
+          <t>FILE DE MERLUZA COSTA SUL 500G CONGELADO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>305039</v>
+        <v>141831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>FILÉ DE PANGA KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>203263</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FILÉ DE TILAPIA KG</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>320788</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HAMBURGUER COSTA SUL 90G SALMÃO</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>323489</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - PEIXES</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>284245</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PEIXITOS COSTA SUL 300G</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMPANADO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>260606</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO COSTA SUL 100G PEIXE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMPANADO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>284246</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>105461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BISTECA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>146785</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LINGUIÇA PERDIGÃO KG SUINA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>189031</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LINGUICA FRICO MISTA KG</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>167154</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LINGUICA FRICÓ KG SUINA FINA APIMENTADA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>106053</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA CARRE KG</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>19.99</v>
+      <c r="C23" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>102242</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>236674</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML ABACAXI CORTELA</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>236672</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML ABORIGENE</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>236671</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML CAJAZINHA</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>236673</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>286589</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>287184</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>286326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>287177</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>215568</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CACHACA BANANAZINHA 900ML</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>174010</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CACHAÇA SELETA 600ML</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>171895</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA ANTARTICA 300ML ORIGINAL </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>170451</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>313599</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>267604</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>303283</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>273004</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENERGETICO ENGOV UP 269ML MELANCIA </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>273000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>273005</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>206930</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GIN TANQUERAY LONDON 750ML</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - FERMENTADOS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>102036</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>137381</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>248750</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>55.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SABADO - PREÇO BALA 17/05/25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>100038</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SABADO - PREÇO BALA 17/05/25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>100031</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>27.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,766 +458,766 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>311307</v>
+        <v>105842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
+          <t>ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15.99</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>303488</v>
+        <v>105838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>118.99</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>323495</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTA SUL 300G COZIDO DECASCADO</t>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.99</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>262170</v>
+        <v>109597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
+          <t>FILE DE PEITO DE FRANGO KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>164651</v>
+        <v>105853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FILE DE MERLUZA COSTA SUL 500G CONGELADO</t>
+          <t>FRANGO MARINGA CONGELADO KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>141831</v>
+        <v>228422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILÉ DE PANGA KG</t>
+          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>203263</v>
+        <v>193650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA KG</t>
+          <t>BATATAS BOUA 400G CONGELADAS PRE-FRITAS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>320788</v>
+        <v>194792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HAMBURGUER COSTA SUL 90G SALMÃO</t>
+          <t>BATATAS BOUA 2KG CONGELADAS PRE-FRITAS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.69</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>323489</v>
+        <v>119923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
+          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>284245</v>
+        <v>104602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PEIXITOS COSTA SUL 300G</t>
+          <t>COXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>260606</v>
+        <v>306504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>STEAK EMPANADO COSTA SUL 100G PEIXE</t>
+          <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.39</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>284246</v>
+        <v>108788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105461</v>
+        <v>309350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BISTECA DO CONTRA FILE KG</t>
+          <t>MASSA DE PASTEL JK 1KG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>31.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>105471</v>
+        <v>108773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>105435</v>
+        <v>261357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>36.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>105474</v>
+        <v>108771</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FRALDINHA BOVINA KG</t>
+          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - EMPANADO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>107260</v>
+        <v>170464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>29.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - EMPANADO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>146785</v>
+        <v>138538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LINGUIÇA PERDIGÃO KG SUINA</t>
+          <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>28.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - EMPANADO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>305039</v>
+        <v>127328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t xml:space="preserve">TEKITOS SEARA 300G QUEIJO OREGANO </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>189031</v>
+        <v>100431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LINGUICA FRICO MISTA KG</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>18.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>167154</v>
+        <v>116139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LINGUICA FRICÓ KG SUINA FINA APIMENTADA</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>26.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>106034</v>
+        <v>107395</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>102242</v>
+        <v>100038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>236674</v>
+        <v>325990</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BEBIDA ALCOOLICA FIU FIU 750ML ABACAXI CORTELA</t>
+          <t xml:space="preserve">ARROZ FLORA PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>44.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>236672</v>
+        <v>100020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BEBIDA ALCOOLICA FIU FIU 750ML ABORIGENE</t>
+          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>44.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>236671</v>
+        <v>273799</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BEBIDA ALCOOLICA FIU FIU 750ML CAJAZINHA</t>
+          <t>ARROZ DELLARROZ PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>236673</v>
+        <v>111378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
+          <t>AZEITONAS LA VIOLETERA 160G VERDES FATIADAS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>286589</v>
+        <v>261728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>287184</v>
+        <v>286197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>286326</v>
+        <v>102085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>287177</v>
+        <v>101137</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>215568</v>
+        <v>287369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>39.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>174010</v>
+        <v>170451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CACHAÇA SELETA 600ML</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>45.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>171895</v>
+        <v>242930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARTICA 300ML ORIGINAL </t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1249,291 +1249,1234 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>170451</v>
+        <v>303283</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>313599</v>
+        <v>101063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 15 X 269ML</t>
+          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>267604</v>
+        <v>123791</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>303283</v>
+        <v>123792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>273004</v>
+        <v>123793</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO ENGOV UP 269ML MELANCIA </t>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>273000</v>
+        <v>123795</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>273005</v>
+        <v>123796</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML ORIGINAL</t>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>206930</v>
+        <v>123797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY LONDON 750ML</t>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>149.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>102036</v>
+        <v>119826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>137381</v>
+        <v>111567</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>129.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>248750</v>
+        <v>110352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>55.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>100038</v>
+        <v>110353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>252617</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>106663</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>113911</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MAÇÃ</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>112163</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MARINE</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>113914</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>102282</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>100780</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>134629</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>100031</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>27.99</v>
+      <c r="C56" t="n">
+        <v>167687</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FEIJÃO JOAOZINHO 1KG CARIOCA PREMIUM</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>111571</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>100120</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>100789</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400G PICANTE</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>100785</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>220451</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO TRIANGULO 395G TP SEMIDESNATADO</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>174382</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEITE EM PO ITALAC 1KG INTEGRAL </t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>170363</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LEITE LEITBOM 1L INTEGRAL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>156422</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>100642</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MACARRÃO PAULISTA 500G SEMOLA ESPAGUETE </t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>274807</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MACARRÃO RICOSA 400G ESPAGUETE COMUM</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>101726</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>234316</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MILHO VERDE SOFRUTA LATA 170G</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>101130</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE </t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>287073</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MOLHO DE TOMATE SABORELLE 300G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>167128</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>128920</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>122984</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE SPRITE 2L</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>104406</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>257710</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>261980</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SABÃO EM PO BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>228234</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>100706</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>221089</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO 125G OLEO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>106831</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TEMPERO SABORELE 930G COMPLETO</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>137423</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VINAGRE SABORELLE 750ML COMPOSTO BRANCO</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>105470</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>152232</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BUCHO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>105468</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>105458</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>105435</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>106053</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="110">
   <si>
     <t>Promoção</t>
   </si>
@@ -31,202 +31,319 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SABADO - FRUTOS DO MAR 17/05/25</t>
-  </si>
-  <si>
-    <t>SABADO - AÇOUGUE 17/05/25</t>
-  </si>
-  <si>
-    <t>SABADO - BIRITAO 17/05/2025</t>
-  </si>
-  <si>
-    <t>SABADO - PREÇO BALA 17/05/25</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - PEIXES</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+    <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+  </si>
+  <si>
+    <t>SEGUNDA - COROCOCO 19/05/25</t>
+  </si>
+  <si>
+    <t>SEGUNDA - OFERTAS 19/05/25</t>
+  </si>
+  <si>
+    <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - AVE</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - EMBUTIDO</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - EMPANADO</t>
   </si>
   <si>
+    <t>#03 LIMPEZA</t>
+  </si>
+  <si>
+    <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - DESTILADOS</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - CERVEJA CX</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - CERVEJA</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - #00 ENERGETICO</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+  </si>
+  <si>
     <t>#06 AÇOUGUE - BOVINO</t>
   </si>
   <si>
-    <t>#06 AÇOUGUE - EMBUTIDO</t>
-  </si>
-  <si>
     <t>#06 AÇOUGUE - SUINO</t>
   </si>
   <si>
-    <t>#05 BEBIDA - DESTILADOS</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - CERVEJA</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - CERVEJA CX</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - #00 ENERGETICO</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - FERMENTADOS</t>
-  </si>
-  <si>
-    <t>#01 MERCEARIA - #01 ALTO GIRO</t>
-  </si>
-  <si>
-    <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
-  </si>
-  <si>
-    <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
-  </si>
-  <si>
-    <t>CAMARÃO COSTA SUL 300G COZIDO DECASCADO</t>
-  </si>
-  <si>
-    <t>COSTELA DE TILAPIA KG</t>
-  </si>
-  <si>
-    <t>FILE DE MERLUZA COSTA SUL 500G CONGELADO</t>
-  </si>
-  <si>
-    <t>FILÉ DE PANGA KG</t>
-  </si>
-  <si>
-    <t>FILÉ DE TILAPIA KG</t>
-  </si>
-  <si>
-    <t>HAMBURGUER COSTA SUL 90G SALMÃO</t>
-  </si>
-  <si>
-    <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
-  </si>
-  <si>
-    <t>PEIXITOS COSTA SUL 300G</t>
-  </si>
-  <si>
-    <t>STEAK EMPANADO COSTA SUL 100G PEIXE</t>
-  </si>
-  <si>
-    <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
-  </si>
-  <si>
-    <t>ALCATRA BOVINA KG</t>
-  </si>
-  <si>
-    <t>BISTECA DO CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>COSTELA BOVINA KG</t>
+    <t>ASA DE FRANGO KG</t>
+  </si>
+  <si>
+    <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+  </si>
+  <si>
+    <t>COXINHA DA ASA DE FRANGO KG</t>
+  </si>
+  <si>
+    <t>FILE DE PEITO DE FRANGO KG</t>
+  </si>
+  <si>
+    <t>FRANGO MARINGA CONGELADO KG</t>
+  </si>
+  <si>
+    <t>GALINHA NOROESTE CONGELADA KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
+  </si>
+  <si>
+    <t>BATATAS BOUA 400G CONGELADAS PRE-FRITAS</t>
+  </si>
+  <si>
+    <t>BATATAS BOUA 2K CONGELADAS PRE-FRITAS</t>
+  </si>
+  <si>
+    <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
+  </si>
+  <si>
+    <t>COXA DE FRANGO SADIA PCT 1KG</t>
+  </si>
+  <si>
+    <t>FIGADO DE FRANGO PERDIGAO KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+  </si>
+  <si>
+    <t>MASSA DE PASTEL JK 1KG</t>
+  </si>
+  <si>
+    <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+  </si>
+  <si>
+    <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
+  </si>
+  <si>
+    <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
+  </si>
+  <si>
+    <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEKITOS SEARA 300G QUEIJO OREGANO </t>
+  </si>
+  <si>
+    <t>AGUA SANITARIA QBOA 2L</t>
+  </si>
+  <si>
+    <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
+  </si>
+  <si>
+    <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARROZ FLORA PCT 5KG TIPO 1 BRANCO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+  </si>
+  <si>
+    <t>ARROZ DELLARROZ PCT 5KG TIPO 1 BRANCO</t>
+  </si>
+  <si>
+    <t>AZEITONAS LA VIOLETERA 160G VERDES FATIADAS</t>
+  </si>
+  <si>
+    <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
+  </si>
+  <si>
+    <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
+  </si>
+  <si>
+    <t>CACHACA 51 965ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+  </si>
+  <si>
+    <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 330ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+  </si>
+  <si>
+    <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L CITRUS</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L FLORAL</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L JASMIM</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2L PINHO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MAÇÃ</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MARINE</t>
+  </si>
+  <si>
+    <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+  </si>
+  <si>
+    <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+  </si>
+  <si>
+    <t>FEIJÃO JOAOZINHO 1KG CARIOCA PREMIUM</t>
+  </si>
+  <si>
+    <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
+  </si>
+  <si>
+    <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+  </si>
+  <si>
+    <t>KETCHUP QUERO 400G PICANTE</t>
+  </si>
+  <si>
+    <t>KETCHUP QUERO 400G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>LEITE CONDENSADO TRIANGULO 395G TP SEMIDESNATADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEITE EM PO ITALAC 1KG INTEGRAL </t>
+  </si>
+  <si>
+    <t>LEITE LEITBOM 1L INTEGRAL</t>
+  </si>
+  <si>
+    <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACARRÃO PAULISTA 500G SEMOLA ESPAGUETE </t>
+  </si>
+  <si>
+    <t>MACARRAO RICOSA 400G ESPAGUETE COMUM</t>
+  </si>
+  <si>
+    <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>MILHO VERDE SOFRUTA LATA 170G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE </t>
+  </si>
+  <si>
+    <t>MOLHO DE TOMATE SABORELLE 300G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>OLEO DE SOJA CONCORDIA 900ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+  </si>
+  <si>
+    <t>REFRIGERANTE SPRITE 2L</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE COCA COLA 2L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
+  </si>
+  <si>
+    <t>SABÃO EM PO BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
+  </si>
+  <si>
+    <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+  </si>
+  <si>
+    <t>SARDINHA COQUEIRO 125G OLEO</t>
+  </si>
+  <si>
+    <t>TEMPERO SABORELE 930G COMPLETO</t>
+  </si>
+  <si>
+    <t>VINAGRE SABORELLE 750ML COMPOSTO BRANCO</t>
+  </si>
+  <si>
+    <t>ACEM BOVINO KG</t>
+  </si>
+  <si>
+    <t>BUCHO BOVINO KG</t>
+  </si>
+  <si>
+    <t>CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>COXÃO DURO KG</t>
   </si>
   <si>
     <t>COXAO MOLE KG</t>
   </si>
   <si>
-    <t>FRALDINHA BOVINA KG</t>
-  </si>
-  <si>
-    <t>MAÇÃ DO PEITO KG</t>
-  </si>
-  <si>
-    <t>LINGUIÇA PERDIGÃO KG SUINA</t>
-  </si>
-  <si>
-    <t>LINGUICA BOVINA CASEIRA KG</t>
-  </si>
-  <si>
-    <t>LINGUICA FRICO MISTA KG</t>
-  </si>
-  <si>
-    <t>LINGUICA FRICÓ KG SUINA FINA APIMENTADA</t>
-  </si>
-  <si>
-    <t>SUAN SUINA KG</t>
-  </si>
-  <si>
-    <t>AGUARDENTE VELHO BARREIRO 910ML</t>
-  </si>
-  <si>
-    <t>BEBIDA ALCOOLICA FIU FIU 750ML ABACAXI CORTELA</t>
-  </si>
-  <si>
-    <t>BEBIDA ALCOOLICA FIU FIU 750ML ABORIGENE</t>
-  </si>
-  <si>
-    <t>BEBIDA ALCOOLICA FIU FIU 750ML CAJAZINHA</t>
-  </si>
-  <si>
-    <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
-  </si>
-  <si>
-    <t>CACHACA BANANAZINHA 900ML</t>
-  </si>
-  <si>
-    <t>CACHAÇA SELETA 600ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERVEJA ANTARTICA 300ML ORIGINAL </t>
-  </si>
-  <si>
-    <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER 15 X 269ML</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENERGETICO ENGOV UP 269ML MELANCIA </t>
-  </si>
-  <si>
-    <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
-  </si>
-  <si>
-    <t>ENERGETICO ENGOV UP 269ML ORIGINAL</t>
-  </si>
-  <si>
-    <t>GIN TANQUERAY LONDON 750ML</t>
-  </si>
-  <si>
-    <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
-  </si>
-  <si>
-    <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
-  </si>
-  <si>
-    <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
+    <t>BISTECA SUINA CARRE KG</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA DO PERNIL KG</t>
   </si>
 </sst>
 </file>
@@ -584,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -612,13 +729,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>311307</v>
+        <v>105842</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
       </c>
       <c r="E2">
-        <v>15.99</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -626,16 +743,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>303488</v>
+        <v>105838</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3">
-        <v>118.99</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -643,16 +760,16 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>323495</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
       </c>
       <c r="E4">
-        <v>36.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -663,13 +780,13 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>262170</v>
+        <v>109597</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
       </c>
       <c r="E5">
-        <v>30.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -680,13 +797,13 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>164651</v>
+        <v>105853</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>27.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -697,13 +814,13 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>141831</v>
+        <v>185934</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
       <c r="E7">
-        <v>39.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -711,101 +828,101 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>203263</v>
+        <v>228422</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
       <c r="E8">
-        <v>49.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>320788</v>
+        <v>193650</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
       <c r="E9">
-        <v>7.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>323489</v>
+        <v>194792</v>
       </c>
       <c r="D10" t="s">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>25.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>284245</v>
+        <v>119923</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
       </c>
       <c r="E11">
-        <v>10.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>260606</v>
+        <v>104602</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
       </c>
       <c r="E12">
-        <v>4.39</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>284246</v>
+        <v>306504</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>10.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -813,16 +930,16 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>105450</v>
+        <v>108788</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14">
-        <v>36.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -830,16 +947,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15">
-        <v>105461</v>
+        <v>309350</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15">
-        <v>31.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -847,16 +964,16 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>105451</v>
+        <v>108773</v>
       </c>
       <c r="D16" t="s">
         <v>36</v>
       </c>
       <c r="E16">
-        <v>36.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -864,16 +981,16 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>105471</v>
+        <v>261357</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
       </c>
       <c r="E17">
-        <v>18.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -881,16 +998,16 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>105435</v>
+        <v>108771</v>
       </c>
       <c r="D18" t="s">
         <v>38</v>
       </c>
       <c r="E18">
-        <v>36.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -901,13 +1018,13 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>105474</v>
+        <v>170464</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
       </c>
       <c r="E19">
-        <v>30.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -918,13 +1035,13 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>107260</v>
+        <v>138538</v>
       </c>
       <c r="D20" t="s">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>29.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -932,84 +1049,84 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>146785</v>
+        <v>127328</v>
       </c>
       <c r="D21" t="s">
         <v>41</v>
       </c>
       <c r="E21">
-        <v>28.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22">
-        <v>305039</v>
+        <v>100431</v>
       </c>
       <c r="D22" t="s">
         <v>42</v>
       </c>
       <c r="E22">
-        <v>15.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23">
-        <v>189031</v>
+        <v>116139</v>
       </c>
       <c r="D23" t="s">
         <v>43</v>
       </c>
       <c r="E23">
-        <v>18.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24">
-        <v>167154</v>
+        <v>107395</v>
       </c>
       <c r="D24" t="s">
         <v>44</v>
       </c>
       <c r="E24">
-        <v>26.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25">
-        <v>106034</v>
+        <v>100038</v>
       </c>
       <c r="D25" t="s">
         <v>45</v>
       </c>
       <c r="E25">
-        <v>13.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1017,16 +1134,16 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26">
-        <v>102242</v>
+        <v>325990</v>
       </c>
       <c r="D26" t="s">
         <v>46</v>
       </c>
       <c r="E26">
-        <v>16.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1034,16 +1151,16 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>236674</v>
+        <v>100020</v>
       </c>
       <c r="D27" t="s">
         <v>47</v>
       </c>
       <c r="E27">
-        <v>44.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1051,16 +1168,16 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>236672</v>
+        <v>273799</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="E28">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1068,16 +1185,16 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>236671</v>
+        <v>111378</v>
       </c>
       <c r="D29" t="s">
         <v>49</v>
       </c>
       <c r="E29">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1085,16 +1202,16 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C30">
-        <v>236673</v>
+        <v>261728</v>
       </c>
       <c r="D30" t="s">
         <v>50</v>
       </c>
       <c r="E30">
-        <v>44.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1102,16 +1219,16 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C31">
-        <v>286589</v>
+        <v>286197</v>
       </c>
       <c r="D31" t="s">
         <v>51</v>
       </c>
       <c r="E31">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1119,16 +1236,16 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>287184</v>
+        <v>102085</v>
       </c>
       <c r="D32" t="s">
         <v>52</v>
       </c>
       <c r="E32">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1136,16 +1253,16 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>286326</v>
+        <v>101137</v>
       </c>
       <c r="D33" t="s">
         <v>53</v>
       </c>
       <c r="E33">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1156,13 +1273,13 @@
         <v>16</v>
       </c>
       <c r="C34">
-        <v>287177</v>
+        <v>287369</v>
       </c>
       <c r="D34" t="s">
         <v>54</v>
       </c>
       <c r="E34">
-        <v>9.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1170,16 +1287,16 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>215568</v>
+        <v>170451</v>
       </c>
       <c r="D35" t="s">
         <v>55</v>
       </c>
       <c r="E35">
-        <v>39.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1187,16 +1304,16 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>174010</v>
+        <v>242930</v>
       </c>
       <c r="D36" t="s">
         <v>56</v>
       </c>
       <c r="E36">
-        <v>45.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1204,16 +1321,16 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C37">
-        <v>171895</v>
+        <v>303283</v>
       </c>
       <c r="D37" t="s">
         <v>57</v>
       </c>
       <c r="E37">
-        <v>4.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1221,16 +1338,16 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C38">
-        <v>170451</v>
+        <v>101063</v>
       </c>
       <c r="D38" t="s">
         <v>58</v>
       </c>
       <c r="E38">
-        <v>2.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1238,16 +1355,16 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>313599</v>
+        <v>123791</v>
       </c>
       <c r="D39" t="s">
         <v>59</v>
       </c>
       <c r="E39">
-        <v>3.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1255,16 +1372,16 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>267604</v>
+        <v>123792</v>
       </c>
       <c r="D40" t="s">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1272,16 +1389,16 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C41">
-        <v>303283</v>
+        <v>123793</v>
       </c>
       <c r="D41" t="s">
         <v>61</v>
       </c>
       <c r="E41">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1289,16 +1406,16 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>273004</v>
+        <v>123795</v>
       </c>
       <c r="D42" t="s">
         <v>62</v>
       </c>
       <c r="E42">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1306,16 +1423,16 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C43">
-        <v>273000</v>
+        <v>123796</v>
       </c>
       <c r="D43" t="s">
         <v>63</v>
       </c>
       <c r="E43">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1323,16 +1440,16 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C44">
-        <v>273005</v>
+        <v>123797</v>
       </c>
       <c r="D44" t="s">
         <v>64</v>
       </c>
       <c r="E44">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1340,16 +1457,16 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45">
-        <v>206930</v>
+        <v>119826</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
       </c>
       <c r="E45">
-        <v>149.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1357,16 +1474,16 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C46">
-        <v>102036</v>
+        <v>111567</v>
       </c>
       <c r="D46" t="s">
         <v>66</v>
       </c>
       <c r="E46">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1374,16 +1491,16 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>137381</v>
+        <v>110352</v>
       </c>
       <c r="D47" t="s">
         <v>67</v>
       </c>
       <c r="E47">
-        <v>129.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1391,50 +1508,730 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48">
-        <v>248750</v>
+        <v>110353</v>
       </c>
       <c r="D48" t="s">
         <v>68</v>
       </c>
       <c r="E48">
-        <v>55.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C49">
-        <v>100038</v>
+        <v>252617</v>
       </c>
       <c r="D49" t="s">
         <v>69</v>
       </c>
       <c r="E49">
-        <v>28.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>100031</v>
+        <v>106663</v>
       </c>
       <c r="D50" t="s">
         <v>70</v>
       </c>
       <c r="E50">
-        <v>27.99</v>
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51">
+        <v>113911</v>
+      </c>
+      <c r="D51" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52">
+        <v>112163</v>
+      </c>
+      <c r="D52" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53">
+        <v>113914</v>
+      </c>
+      <c r="D53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <v>102282</v>
+      </c>
+      <c r="D54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55">
+        <v>100780</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>134629</v>
+      </c>
+      <c r="D56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57">
+        <v>167687</v>
+      </c>
+      <c r="D57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>111571</v>
+      </c>
+      <c r="D58" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <v>100120</v>
+      </c>
+      <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60">
+        <v>100789</v>
+      </c>
+      <c r="D60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61">
+        <v>100785</v>
+      </c>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62">
+        <v>220451</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>174382</v>
+      </c>
+      <c r="D63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64">
+        <v>170363</v>
+      </c>
+      <c r="D64" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65">
+        <v>156422</v>
+      </c>
+      <c r="D65" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66">
+        <v>100642</v>
+      </c>
+      <c r="D66" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>274807</v>
+      </c>
+      <c r="D67" t="s">
+        <v>86</v>
+      </c>
+      <c r="E67">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>101726</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69">
+        <v>234316</v>
+      </c>
+      <c r="D69" t="s">
+        <v>88</v>
+      </c>
+      <c r="E69">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>101130</v>
+      </c>
+      <c r="D70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71">
+        <v>287073</v>
+      </c>
+      <c r="D71" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>167128</v>
+      </c>
+      <c r="D72" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73">
+        <v>128920</v>
+      </c>
+      <c r="D73" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74">
+        <v>122984</v>
+      </c>
+      <c r="D74" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75">
+        <v>104406</v>
+      </c>
+      <c r="D75" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76">
+        <v>257710</v>
+      </c>
+      <c r="D76" t="s">
+        <v>95</v>
+      </c>
+      <c r="E76">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77">
+        <v>261980</v>
+      </c>
+      <c r="D77" t="s">
+        <v>96</v>
+      </c>
+      <c r="E77">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78">
+        <v>228234</v>
+      </c>
+      <c r="D78" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79">
+        <v>100706</v>
+      </c>
+      <c r="D79" t="s">
+        <v>98</v>
+      </c>
+      <c r="E79">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80">
+        <v>221089</v>
+      </c>
+      <c r="D80" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81">
+        <v>106831</v>
+      </c>
+      <c r="D81" t="s">
+        <v>100</v>
+      </c>
+      <c r="E81">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82">
+        <v>137423</v>
+      </c>
+      <c r="D82" t="s">
+        <v>101</v>
+      </c>
+      <c r="E82">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
+        <v>105470</v>
+      </c>
+      <c r="D83" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>152232</v>
+      </c>
+      <c r="D84" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>105468</v>
+      </c>
+      <c r="D85" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86">
+        <v>105458</v>
+      </c>
+      <c r="D86" t="s">
+        <v>105</v>
+      </c>
+      <c r="E86">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87">
+        <v>105449</v>
+      </c>
+      <c r="D87" t="s">
+        <v>106</v>
+      </c>
+      <c r="E87">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88">
+        <v>105435</v>
+      </c>
+      <c r="D88" t="s">
+        <v>107</v>
+      </c>
+      <c r="E88">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89">
+        <v>106053</v>
+      </c>
+      <c r="D89" t="s">
+        <v>108</v>
+      </c>
+      <c r="E89">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90">
+        <v>105062</v>
+      </c>
+      <c r="D90" t="s">
+        <v>109</v>
+      </c>
+      <c r="E90">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,858 +458,858 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105842</v>
+        <v>157014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t>ACEM BOVINO COM OSSO KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105838</v>
+        <v>105461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t>BISTECA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11.69</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105840</v>
+        <v>105468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14.39</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>109597</v>
+        <v>105451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
+          <t>CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19.89</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105853</v>
+        <v>105449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.89</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>228422</v>
+        <v>173342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
+          <t>MOCOTO BOVINO KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>193650</v>
+        <v>105452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BATATAS BOUA 400G CONGELADAS PRE-FRITAS</t>
+          <t>PATINHO BOVINO KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>194792</v>
+        <v>105853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BATATAS BOUA 2KG CONGELADAS PRE-FRITAS</t>
+          <t>FRANGO MARINGA CONGELADO KG</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>119923</v>
+        <v>305039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104602</v>
+        <v>105765</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COXA DE FRANGO SADIA PCT 1KG</t>
+          <t>MORTADELA PERDIGAO MISTA KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>306504</v>
+        <v>239921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FIGADO DE FRANGO PERDIGAO KG</t>
+          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.49</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>108788</v>
+        <v>106054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+          <t>LOMBO SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>309350</v>
+        <v>106034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MASSA DE PASTEL JK 1KG</t>
+          <t>SUAN SUINA KG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>108773</v>
+        <v>255232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>261357</v>
+        <v>100426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PEITO DE FRANGO SADIA 400G DESFIADO</t>
+          <t>AGUA SANITARIA QBOA 1L</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>16.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>108771</v>
+        <v>181416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
+          <t>AMACIANTE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>170464</v>
+        <v>136523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.19</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>138538</v>
+        <v>225003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
+          <t xml:space="preserve">ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>127328</v>
+        <v>100031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEKITOS SEARA 300G QUEIJO OREGANO </t>
+          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.49</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100431</v>
+        <v>326645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 2L</t>
+          <t>ARROZ SEU ARROZ PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.19</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>116139</v>
+        <v>250013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
+          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>107395</v>
+        <v>286746</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
+          <t xml:space="preserve">BISCOITO SULLPER 600G ROSQUINHA COCO </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.49</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100038</v>
+        <v>239682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">BOMBOM GAROTO CAIXA 250G SORTIDO </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>325990</v>
+        <v>102085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ FLORA PCT 5KG TIPO 1 BRANCO </t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100020</v>
+        <v>101137</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REALENGO PCT 5KG TIPO 1 BRANCO </t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>273799</v>
+        <v>287369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ARROZ DELLARROZ PCT 5KG TIPO 1 BRANCO</t>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>111378</v>
+        <v>170451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AZEITONAS LA VIOLETERA 160G VERDES FATIADAS</t>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>261728</v>
+        <v>247800</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350G CREAM CRACKER</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML LARGER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8.19</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>286197</v>
+        <v>267604</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102085</v>
+        <v>303282</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>101137</v>
+        <v>220499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>CORONA EXTRA 330ML LONG NECK</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>287369</v>
+        <v>106866</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+          <t>CREME DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>170451</v>
+        <v>101066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>CREME DE LEITE ITALAC 200G</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>242930</v>
+        <v>112978</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>303283</v>
+        <v>208281</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>101063</v>
+        <v>208304</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML PROTECT UNISSEX </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>123791</v>
+        <v>208280</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>123792</v>
+        <v>142863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+          <t>DESINFETANTE YPE BAK 2L LAVANDA</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>123793</v>
+        <v>134193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+          <t>DESINFETANTE YPE BAK 2L FLORAL</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1364,402 +1364,402 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>123795</v>
+        <v>254080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+          <t>DESINFETANTE YPÊ BAK 2L LAVANDA PROMOCIONAL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>123796</v>
+        <v>312369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML ENERGY MEN </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>123797</v>
+        <v>312371</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L PINHO</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO FLOR LAVANDA </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>119826</v>
+        <v>312370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>111567</v>
+        <v>312366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE PROTECT </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>110352</v>
+        <v>312367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FRUTAS VERMELHA </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>110353</v>
+        <v>312368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML POWER MEN </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>252617</v>
+        <v>298933</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML INVISIBLE CARE </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>106663</v>
+        <v>298932</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN SPORT </t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>113911</v>
+        <v>298931</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MAÇÃ</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML UNISSEX SPORT </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>112163</v>
+        <v>298930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MARINE</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML SEM PERFUME </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>113914</v>
+        <v>298929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN GIRL </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>102282</v>
+        <v>298928</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN SPORT </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100780</v>
+        <v>298927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN BOY </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>134629</v>
+        <v>311881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO </t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATAÇÃO INTENSA </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>167687</v>
+        <v>100391</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FEIJÃO JOAOZINHO 1KG CARIOCA PREMIUM</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>111571</v>
+        <v>100394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100120</v>
+        <v>100392</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1769,168 +1769,168 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>100789</v>
+        <v>100402</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400G PICANTE</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>100785</v>
+        <v>100403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400G TRADICIONAL</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>220451</v>
+        <v>100393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO TRIANGULO 395G TP SEMIDESNATADO</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>174382</v>
+        <v>100390</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO ITALAC 1KG INTEGRAL </t>
+          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>37.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>170363</v>
+        <v>312365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LEITE LEITBOM 1L INTEGRAL</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FLOR DE ALGODAO WOMEN </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.29</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>156422</v>
+        <v>312364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LIMPADOR VEJA MULTI USO PROMOCIONAL 500ML</t>
+          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML IMPACT MEN </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>100642</v>
+        <v>102287</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRÃO PAULISTA 500G SEMOLA ESPAGUETE </t>
+          <t>ENERGETICO EXTRA POWER 270ML</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1939,21 +1939,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>274807</v>
+        <v>273714</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MACARRÃO RICOSA 400G ESPAGUETE COMUM</t>
+          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>101726</v>
+        <v>100110</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500G TRADICIONAL</t>
+          <t>FARINHA DE MILHO SINHA 500G BIJU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1985,67 +1985,67 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>234316</v>
+        <v>100027</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MILHO VERDE SOFRUTA LATA 170G</t>
+          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3.79</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>101130</v>
+        <v>100014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MISTURA PARA BOLOS DONA BENTA 450G CHOCOLATE </t>
+          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>287073</v>
+        <v>163918</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MOLHO DE TOMATE SABORELLE 300G TRADICIONAL</t>
+          <t>FEIJÃO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>167128</v>
+        <v>140665</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+          <t xml:space="preserve">FEIJAO KICALDO 1KG RETO </t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8.59</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2077,136 +2077,136 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>128920</v>
+        <v>111571</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLVILHO MATUTO 1KG DOCE </t>
+          <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8.99</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>122984</v>
+        <v>100119</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>REFRIGERANTE SPRITE 2L</t>
+          <t>FLOCÃO DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>104406</v>
+        <v>139059</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>LAVA LOUÇAS LIQUIDO YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>10.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>257710</v>
+        <v>108434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
+          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>261980</v>
+        <v>174382</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SABÃO EM PO BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
+          <t xml:space="preserve">LEITE EM PO ITALAC 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>20.99</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>228234</v>
+        <v>307145</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
+          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>13.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2215,21 +2215,21 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>100706</v>
+        <v>251877</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDINHA COQUEIRO 125G MOLHO DE TOMATE </t>
+          <t>LEITE PO NINHO LATA 380G INTEGRAL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5.69</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>221089</v>
+        <v>303196</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125G OLEO</t>
+          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>106831</v>
+        <v>149122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELE 930G COMPLETO</t>
+          <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>11.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2284,199 +2284,176 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>137423</v>
+        <v>234626</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VINAGRE SABORELLE 750ML COMPOSTO BRANCO</t>
+          <t>MILHO VERDE BONARE LATA 170G</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.39</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>105470</v>
+        <v>106680</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>23.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>152232</v>
+        <v>104403</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>14.99</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>105468</v>
+        <v>104410</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>17.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>105458</v>
+        <v>104406</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>18.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>105449</v>
+        <v>257710</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>32.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>105435</v>
+        <v>248450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>36.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>106053</v>
+        <v>100373</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BISTECA SUINA CARRE KG</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - SUINO</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>105062</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>18.99</v>
+        <v>24.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,237 +458,237 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157014</v>
+        <v>105007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
+          <t>ABOBORA KG CABOTIA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105461</v>
+        <v>104937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BISTECA DO CONTRA FILE KG</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105468</v>
+        <v>105023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105451</v>
+        <v>104998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>BANANA DA TERRA KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105449</v>
+        <v>104903</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>BATATA DOCE KG ROSA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>173342</v>
+        <v>105010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MOCOTO BOVINO KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105452</v>
+        <v>105001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PATINHO BOVINO KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105853</v>
+        <v>104919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>305039</v>
+        <v>104862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>105765</v>
+        <v>104931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MORTADELA PERDIGAO MISTA KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -697,770 +697,770 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239921</v>
+        <v>104944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106054</v>
+        <v>104928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LOMBO SUINO FRESCO KG</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>18.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>106034</v>
+        <v>104883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t xml:space="preserve">MANGA KG TOMY </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>255232</v>
+        <v>104947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100426</v>
+        <v>104996</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 1L</t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>181416</v>
+        <v>113290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS YPE 2L ACONCHEGO PROMOCIONAL</t>
+          <t xml:space="preserve">MELAO AMARELO KG REI | REDINHA </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>136523</v>
+        <v>104992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ KOBLENZ PCT 5KG TIPO 1 BRANCO </t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>27.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>225003</v>
+        <v>104961</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO </t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>23.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100031</v>
+        <v>104890</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO </t>
+          <t>UVA KG RED GLOBE NACIONAL</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>326645</v>
+        <v>105460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ PCT 5KG TIPO 1 BRANCO</t>
+          <t>BISTECA BOVINA KG PALETA</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>250013</v>
+        <v>105450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+          <t>ALCATRA BOVINA KG</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>286746</v>
+        <v>105459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO SULLPER 600G ROSQUINHA COCO </t>
+          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.19</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>239682</v>
+        <v>239334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOMBOM GAROTO CAIXA 250G SORTIDO </t>
+          <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>102085</v>
+        <v>105468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>101137</v>
+        <v>105435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>COXAO MOLE KG</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>287369</v>
+        <v>107260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.49</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>170451</v>
+        <v>305039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.89</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>247800</v>
+        <v>105062</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER LONG NECK 330ML LARGER</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>267604</v>
+        <v>106032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
+          <t>TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>303282</v>
+        <v>318330</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK</t>
+          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>220499</v>
+        <v>100431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CORONA EXTRA 330ML LONG NECK</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>106866</v>
+        <v>102242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CREME DE MILHO SINHA 500G</t>
+          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>101066</v>
+        <v>116139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CREME DE LEITE ITALAC 200G</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>112978</v>
+        <v>107395</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500G</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.69</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>208281</v>
+        <v>100038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN </t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>208304</v>
+        <v>148775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML PROTECT UNISSEX </t>
+          <t>ARROZ PIANTA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>208280</v>
+        <v>199440</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN </t>
+          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>142863</v>
+        <v>100040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPE BAK 2L LAVANDA</t>
+          <t>ARROZ TIO JORGE PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>134193</v>
+        <v>250013</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPE BAK 2L FLORAL</t>
+          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>254080</v>
+        <v>286197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DESINFETANTE YPÊ BAK 2L LAVANDA PROMOCIONAL</t>
+          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>312369</v>
+        <v>114037</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML ENERGY MEN </t>
+          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>312371</v>
+        <v>252992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO FLOR LAVANDA </t>
+          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>312370</v>
+        <v>298701</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE </t>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>312366</v>
+        <v>242930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATANTE PROTECT </t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1470,237 +1470,237 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>312367</v>
+        <v>110330</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FRUTAS VERMELHA </t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>312368</v>
+        <v>123791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML POWER MEN </t>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>298933</v>
+        <v>123792</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML INVISIBLE CARE </t>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>298932</v>
+        <v>123793</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML WOMEN SPORT </t>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>298931</v>
+        <v>123795</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML UNISSEX SPORT </t>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>298930</v>
+        <v>123796</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML SEM PERFUME </t>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>298929</v>
+        <v>123797</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN GIRL </t>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>298928</v>
+        <v>100423</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML MEN SPORT </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>298927</v>
+        <v>100419</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML TEEN BOY </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>311881</v>
+        <v>220037</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FEMININO HIDRATAÇÃO INTENSA </t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1709,21 +1709,21 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>100391</v>
+        <v>204461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CAPIM LIMAO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>100394</v>
+        <v>100420</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100392</v>
+        <v>100417</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML CLEAR CARE</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1778,297 +1778,297 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>100402</v>
+        <v>106661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML COCO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>100403</v>
+        <v>167686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML LIMAO</t>
+          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.69</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>100393</v>
+        <v>100014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML MACA</t>
+          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>100390</v>
+        <v>106922</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO YPE 500ML NEUTRO</t>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.69</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>312365</v>
+        <v>131884</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML FLOR DE ALGODAO WOMEN </t>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6.99</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>312364</v>
+        <v>130920</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DESODORANTE MOOD AEROSOL 150ML IMPACT MEN </t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 ENERGETICO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>102287</v>
+        <v>167128</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML</t>
+          <t>OLEO DE SOJA CONCORDIA 900ML</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>273714</v>
+        <v>316048</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
+          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>100110</v>
+        <v>326954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FARINHA DE MILHO SINHA 500G BIJU</t>
+          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>100027</v>
+        <v>289451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO </t>
+          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7.69</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>100014</v>
+        <v>228234</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>163918</v>
+        <v>106831</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FEIJÃO KICALDO 1KG CARIOCA</t>
+          <t>TEMPERO SABORELE 930G COMPLETO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6.99</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>140665</v>
+        <v>111010</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJAO KICALDO 1KG RETO </t>
+          <t>TEMPERO SABORELLE 930G COMPLETO SEM PIMENTA</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8.390000000000001</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2077,383 +2077,15 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>111571</v>
+        <v>100884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
+          <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>100119</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>FLOCÃO DE MILHO SINHA 500G</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>139059</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LAVA LOUÇAS LIQUIDO YPE 500ML LIMAO</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>108434</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LEITE CONDENSADO ITALAC 395G SEMIDESNATADO </t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>174382</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LEITE EM PO ITALAC 1KG INTEGRAL </t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>307145</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LEITE EM PO NINHO 380G INTEGRAL INSTANTANEL </t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>251877</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LEITE PO NINHO LATA 380G INTEGRAL</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>303196</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MACARRAO GALO 400G ESPAGUETE AMARELO </t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>149122</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>234626</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>MILHO VERDE BONARE LATA 170G</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>106680</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>OLEO DE SOJA SOYA 900ML</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>104403</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L UVA </t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>9.390000000000001</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>104410</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>104406</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>257710</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SABÃO EM BARRA YPE 900G NEUTRO </t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>248450</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA </t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>100373</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>24.99</v>
+        <v>5.49</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.49</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="5">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="8">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="11">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="13">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>104992</v>
+        <v>239921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.99</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="19">
@@ -858,15 +858,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104961</v>
+        <v>104992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="20">
@@ -881,38 +881,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>104890</v>
+        <v>104961</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UVA KG RED GLOBE NACIONAL</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#09 HORTIFRUTI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>105460</v>
+        <v>104890</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
+          <t>UVA KG RED GLOBE NACIONAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="22">
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105450</v>
+        <v>105460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ALCATRA BOVINA KG</t>
+          <t>BISTECA BOVINA KG PALETA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="23">
@@ -950,15 +950,15 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>105459</v>
+        <v>105450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
+          <t>ALCATRA BOVINA KG</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="24">
@@ -973,15 +973,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>239334</v>
+        <v>105459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAPA DO CONTRA FILE KG</t>
+          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>26.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="25">
@@ -996,15 +996,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>105468</v>
+        <v>239334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="26">
@@ -1019,15 +1019,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>105435</v>
+        <v>105468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="27">
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>107260</v>
+        <v>105435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>COXAO MOLE KG</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>29.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="28">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>305039</v>
+        <v>107260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="29">
@@ -1084,19 +1084,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>105062</v>
+        <v>305039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="30">
@@ -1111,11 +1111,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>106032</v>
+        <v>105062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1125,24 +1125,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>318330</v>
+        <v>106032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
+          <t>TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="32">
@@ -1153,19 +1153,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>100431</v>
+        <v>318330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 2L</t>
+          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.19</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="33">
@@ -1176,19 +1176,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>102242</v>
+        <v>100431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="34">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>116139</v>
+        <v>102242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
+          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7.39</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="35">
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>107395</v>
+        <v>116139</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1245,19 +1245,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>100038</v>
+        <v>107395</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>27.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="37">
@@ -1272,15 +1272,15 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>148775</v>
+        <v>100038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ARROZ PIANTA PCT 5KG TIPO 1 BRANCO</t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="38">
@@ -1295,15 +1295,15 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>199440</v>
+        <v>148775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+          <t>ARROZ PIANTA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="39">
@@ -1318,15 +1318,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100040</v>
+        <v>199440</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ARROZ TIO JORGE PCT 5KG TIPO 1 BRANCO</t>
+          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="40">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>250013</v>
+        <v>100040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+          <t>ARROZ TIO JORGE PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6.59</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="41">
@@ -1364,15 +1364,15 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>286197</v>
+        <v>250013</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
+          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="42">
@@ -1387,15 +1387,15 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>114037</v>
+        <v>286197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
+          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="43">
@@ -1410,15 +1410,15 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>252992</v>
+        <v>114037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
+          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="44">
@@ -1429,19 +1429,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>298701</v>
+        <v>252992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4.19</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="45">
@@ -1452,19 +1452,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>242930</v>
+        <v>298701</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="46">
@@ -1475,19 +1475,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>110330</v>
+        <v>242930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
@@ -1498,19 +1498,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>123791</v>
+        <v>110330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>11.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="48">
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>123792</v>
+        <v>123791</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+          <t>DESINFETANTE START VOREL 2L CITRUS</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1548,11 +1548,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>123793</v>
+        <v>123792</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>123795</v>
+        <v>123793</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+          <t>DESINFETANTE START VOREL 2L FLORAL</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>123796</v>
+        <v>123795</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
+          <t>DESINFETANTE START VOREL 2L JASMIM</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1617,11 +1617,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>123797</v>
+        <v>123796</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L PINHO</t>
+          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1640,15 +1640,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>100423</v>
+        <v>123797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
+          <t>DESINFETANTE START VOREL 2L PINHO</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.59</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="54">
@@ -1663,11 +1663,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100419</v>
+        <v>100423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>220037</v>
+        <v>100419</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1709,11 +1709,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>204461</v>
+        <v>220037</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>100420</v>
+        <v>204461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1755,11 +1755,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100417</v>
+        <v>100420</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>106661</v>
+        <v>100417</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>167686</v>
+        <v>106661</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5.89</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="61">
@@ -1824,15 +1824,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>100014</v>
+        <v>167686</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
+          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="62">
@@ -1843,19 +1843,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>106922</v>
+        <v>100014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
+          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="63">
@@ -1870,15 +1870,15 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>131884</v>
+        <v>106922</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.39</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="64">
@@ -1893,15 +1893,15 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>130920</v>
+        <v>131884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
+          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.89</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="65">
@@ -1912,19 +1912,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>167128</v>
+        <v>130920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8.789999999999999</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="66">
@@ -1935,19 +1935,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>316048</v>
+        <v>167128</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
+          <t>OLEO DE SOJA CONCORDIA 900ML</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>17.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1958,19 +1958,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>326954</v>
+        <v>316048</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
+          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="68">
@@ -1985,15 +1985,15 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>289451</v>
+        <v>326954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
+          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>29.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="69">
@@ -2008,15 +2008,15 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>228234</v>
+        <v>289451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
+          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>13.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="70">
@@ -2027,19 +2027,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>106831</v>
+        <v>228234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELE 930G COMPLETO</t>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>11.49</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="71">
@@ -2054,11 +2054,11 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>111010</v>
+        <v>106831</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELLE 930G COMPLETO SEM PIMENTA</t>
+          <t>TEMPERO SABORELE 930G COMPLETO</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2077,14 +2077,37 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>111010</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TEMPERO SABORELLE 930G COMPLETO SEM PIMENTA</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QUARTA - OFERTAS 21/05/25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
         <v>100884</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E73" t="n">
         <v>5.49</v>
       </c>
     </row>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ofertas Corrigidas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,697 +458,681 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105007</v>
+        <v>258938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ABOBORA KG CABOTIA</t>
+          <t>ARROZ BRILHANTE PCT 5KG</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>104937</v>
+        <v>269680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>ARROZ DONA VAVA PCT 5KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105023</v>
+        <v>100020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>ARROZ REALENGO PCT 5KG</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.59</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>104998</v>
+        <v>326645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BANANA DA TERRA KG</t>
+          <t>ARROZ SEU ARROZ PCT 5KG</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>104903</v>
+        <v>100014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BATATA DOCE KG ROSA</t>
+          <t>FEIJÃO GOL 1KG</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>105010</v>
+        <v>100013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>FEIJÃO TIO JORGE 1KG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.89</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105001</v>
+        <v>298239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>AÇUCAR ECOÇUCAR CRISTAL 2KG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#01 MERCEARIA - #02 ALTO GIRO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104919</v>
+        <v>106680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>OLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5.49</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104931</v>
+        <v>130107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>AZEITE DE OLIVA COCINERO 500ML</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.390000000000001</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104944</v>
+        <v>250013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>BISCOITO MARILAN 350G</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.39</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104928</v>
+        <v>257157</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>BISCOITO MICOS 600G</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>104883</v>
+        <v>305475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANGA KG TOMY </t>
+          <t>CAFÉ UNIÃO 250G</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>104947</v>
+        <v>101063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>CREME DE LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.79</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>104996</v>
+        <v>112978</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>113290</v>
+        <v>100780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELAO AMARELO KG REI | REDINHA </t>
+          <t>EXTRATO DE TOMATE OLE COPO 190G</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>239921</v>
+        <v>324143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
+          <t>FARINHA DE MANDIOCA OVINHA DONA DE 1KG</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.65</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104992</v>
+        <v>100110</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>FARINHA DE MILHO SINHA 500G</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>104961</v>
+        <v>100027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>FARINHA DE TRIGO ORQUIDEA 1KG</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.49</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>104890</v>
+        <v>111571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UVA KG RED GLOBE NACIONAL</t>
+          <t>FLOCAO DE ARROZ BONOARROZ 500G</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105460</v>
+        <v>255841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
+          <t>FLOCÃO DE MILHO AMAFIL 500G</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>105450</v>
+        <v>113183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ALCATRA BOVINA KG</t>
+          <t>LEITE CONDENSADO MARAJOARA 395G</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>105459</v>
+        <v>106922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
+          <t>LEITE EM PO CCGL 1KG</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21.99</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>239334</v>
+        <v>219003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAPA DO CONTRA FILE KG</t>
+          <t>LEITE ITALAC 1L</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>26.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>105468</v>
+        <v>303196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>MACARRAO GALO 400G</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>105435</v>
+        <v>101726</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>MAIONESE ARISCO 500G</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>34.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>107260</v>
+        <v>149121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>MASSA PARA TAPIOCA AMAFIL 500G</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>29.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>305039</v>
+        <v>107640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>MILHO VERDE QUERO LATA 170G</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>105062</v>
+        <v>321107</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>MOLHO QUERO PRONTO SACHÊ 240G</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>106032</v>
+        <v>128920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t>POLVILHO MATUTO 1KG</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>18.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1157,90 +1141,74 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>318330</v>
+        <v>263553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
+          <t>ROSQUINHA MICOS 600G</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>100431</v>
+        <v>286325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA QBOA 2L</t>
+          <t>SUCO DE UVA AURORA TP 1,5L</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7.19</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>102242</v>
+        <v>100884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+          <t>TEMPERO EM PÓ SAZON SACHÊ 60G</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15.99</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>116139</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>7.39</v>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1249,11 +1217,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>107395</v>
+        <v>100431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L ROSAS</t>
+          <t>AGUA SANITARIA QBOA 2L</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1263,572 +1231,540 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100038</v>
+        <v>248717</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>DESINFETANTE POLITRIZ 1,75L</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>27.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>148775</v>
+        <v>100391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ARROZ PIANTA PCT 5KG TIPO 1 BRANCO</t>
+          <t>DETERGENTE LIQUIDO YPE 500ML</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>199440</v>
+        <v>260659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ SANTA FE PCT 5KG TIPO 1 BRANCO </t>
+          <t>LIMPADOR QBOA 500ML</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>19.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>100040</v>
+        <v>320166</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ARROZ TIO JORGE PCT 5KG TIPO 1 BRANCO</t>
+          <t>PAPEL TOALHA ABSOLUTO 2 X 240 FOLHAS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250013</v>
+        <v>292093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISCOITO MARILAN 350G CRACKER ESPECIAL </t>
+          <t>SABÃO BARRA ESTRELA 900G</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.59</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>286197</v>
+        <v>326954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600G ROSQUINHA COCO</t>
+          <t>SABÃO EM BARRA REGENTE 5X 200G</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>114037</v>
+        <v>296910</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE SANTA CLARA 250G CLASSICO </t>
+          <t>SABÃO EM PO ASSIM 800G</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>15.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>252992</v>
+        <v>286199</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CEREAL KELLOGS 240G SUCRILHOS ORIGINAL</t>
+          <t>SABÃO EM PO TIXAN YPE CAIXA 800G</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>13.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#03 LIMPEZA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>298701</v>
+        <v>100373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4.19</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - CERVEJA</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>242930</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>6.99</v>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>110330</v>
+        <v>235809</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500G</t>
+          <t>CREME DENTAL SORRISO 120G</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.19</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>123791</v>
+        <v>304353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L CITRUS</t>
+          <t>ENXAGUANTE BUCAL CEPACOL 500ML</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>11.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>123792</v>
+        <v>322795</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L EUCALIPTO</t>
+          <t>PAPEL HIGIENICO ONDUNORTE 12 X 20M</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>123793</v>
+        <v>144261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L FLORAL</t>
+          <t>SABONETE PALMOLIVE 150G</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#04 HIGIENE PESSOAL</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>123795</v>
+        <v>114072</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L JASMIM</t>
+          <t>TALCO TABU 100G</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>123796</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>11.99</v>
-      </c>
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>123797</v>
+        <v>315650</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2L PINHO</t>
+          <t>ENERGETICO BALY 250ML</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100423</v>
+        <v>253879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML COCO</t>
+          <t>ENERGETICO BALY LATA 250ML</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>100419</v>
+        <v>273004</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML CRISTAL</t>
+          <t>ENERGETICO ENGOV UP 269ML</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>220037</v>
+        <v>102282</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML JABOTICABA</t>
+          <t>ENERGETICO RED BULL 250ML</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>204461</v>
+        <v>104406</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LAVANDA</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.59</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100420</v>
+        <v>104403</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML LIMÃO</t>
+          <t>REFRIGERANTE FANTA 2L</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.59</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>100417</v>
+        <v>104414</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML MAÇÃ</t>
+          <t>REFRIGERANTE SUKITA 2L</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.59</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>106661</v>
+        <v>259589</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML NEUTRO</t>
+          <t>CERVEJA STELLA ARTOIS 600ML</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.59</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>167686</v>
+        <v>303283</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FEIJÃO KI SABOR 1KG CARIOCA</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1838,277 +1774,353 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>100014</v>
+        <v>265727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
+          <t>CERVEJA HEINEKEN 8 X 269ML</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>106922</v>
+        <v>293188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEITE EM PO CCGL 1KG INTEGRAL </t>
+          <t>CACHACA 51 600ML</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>42.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>131884</v>
+        <v>215568</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARRAO GALO 500G ESPAGUETE VERMELHO Nº8 </t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.39</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>130920</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MILHO VERDE FUGINI LATA 200G VAPOR </t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>3.89</v>
-      </c>
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>167128</v>
+        <v>105458</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+          <t>CHAMBARI KG</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8.789999999999999</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#04 HIGIENE PESSOAL</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>316048</v>
+        <v>105449</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 12 X 30M PROMOCIONAL SOFT B</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>17.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>326954</v>
+        <v>115278</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
+          <t>MIOLO DA PALETA KG BOVINA</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>8.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>289451</v>
+        <v>231292</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABAO EM PO +CASA SACHE 5KG MULTIACAO </t>
+          <t>MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>29.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>228234</v>
+        <v>305039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>13.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>106831</v>
+        <v>106053</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELE 930G COMPLETO</t>
+          <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>111010</v>
+        <v>105062</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TEMPERO SABORELLE 930G COMPLETO SEM PIMENTA</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>11.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>100884</v>
+        <v>105433</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5.49</v>
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>106054</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LOMBO SUINO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>258810</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PANCETA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>106050</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PE SUINO KG</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>106052</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PELE SUINA KG</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -429,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -469,140 +469,92 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>152232</v>
+        <v>100038</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>105458</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>18.99</v>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#02 MERCEARIA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>105471</v>
+        <v>101137</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>105474</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>FRALDINHA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>30.99</v>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>105467</v>
+        <v>107376</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>LINGUA BOVINA KG</t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>11.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>107260</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>MAÇÃ DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>29.99</v>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -616,15 +568,15 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>173342</v>
+        <v>152232</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MOCOTO BOVINO KG</t>
+          <t>BUCHO BOVINO KG</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +587,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>305039</v>
+        <v>105458</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>CHAMBARI KG</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>16.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
@@ -658,18 +610,156 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>105467</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>LINGUA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>107260</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>173342</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>MOCOTO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>106008</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>18.99</v>
       </c>
     </row>

--- a/ofertas_corrigidas.xlsx
+++ b/ofertas_corrigidas.xlsx
@@ -429,14 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,212 +469,244 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>100038</v>
+        <v>286589</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO </t>
+          <t>BEBIDA ENGOV AFTER 250ML</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>27.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>171895</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA ANTARTICA 300ML ORIGINAL </t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4.59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>#02 MERCEARIA</t>
+          <t>#05 BEBIDA - CERVEJA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>101137</v>
+        <v>267604</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFE MARATA 250G TRADICIONAL </t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>313599</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3.69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA CX</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>107376</v>
+        <v>102242</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
+          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>236674</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>BEBIDA ALCOOLICA FIU FIU 750ML</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>44.99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>152232</v>
+        <v>174010</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>CACHAÇA SELETA 600ML</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>16.99</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>105458</v>
+        <v>206930</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>GIN TANQUERAY LONDON 750ML</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>18.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>105471</v>
+        <v>137381</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>18.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>105474</v>
+        <v>248750</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>FRALDINHA BOVINA KG</t>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>30.99</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>105467</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>LINGUA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>11.99</v>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -683,21 +715,21 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>107260</v>
+        <v>105461</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>BISTECA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>29.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -706,61 +738,222 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>173342</v>
+        <v>105468</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MOCOTO BOVINO KG</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>305039</v>
+        <v>105451</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>16.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>106008</v>
+        <v>105471</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INGREDIENTES PARA FEIJOADA KG</t>
+          <t>COSTELA BOVINA KG</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>18.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>105474</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>FRALDINHA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>106053</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>105062</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>106008</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>
